--- a/public/sample/rider_invoice_sample.xlsx
+++ b/public/sample/rider_invoice_sample.xlsx
@@ -1,31 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAUD AHMAD\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75813ED1-A652-492C-BF00-9DD4382928BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="73">
+  <si>
+    <t>Invoice Date</t>
+  </si>
   <si>
     <t>ID</t>
   </si>
@@ -33,237 +26,233 @@
     <t>Rider_Name</t>
   </si>
   <si>
+    <t>Rejection</t>
+  </si>
+  <si>
+    <t>Login Hours</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>Working Days</t>
+  </si>
+  <si>
+    <t>Perf_Attendance</t>
+  </si>
+  <si>
+    <t>Off</t>
+  </si>
+  <si>
+    <t>Performance</t>
+  </si>
+  <si>
     <t>Billing Month</t>
   </si>
   <si>
-    <t>Invoice Date</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>If you have any discrepancies regarding this invoice, you may contact our Accounts Department within 4 days. After this period, no changes will be accepted.</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Unpaid</t>
-  </si>
-  <si>
-    <t>Delivery fees</t>
-  </si>
-  <si>
-    <t>Guaranteed subsidy</t>
-  </si>
-  <si>
-    <t>Attendance incentive</t>
-  </si>
-  <si>
-    <t>Activity rewards</t>
-  </si>
-  <si>
-    <t>Flexible subsidy</t>
-  </si>
-  <si>
-    <t>Other Rewards</t>
-  </si>
-  <si>
-    <t>food compensation</t>
-  </si>
-  <si>
-    <t>Deduction</t>
-  </si>
-  <si>
-    <t>Tips(VAT Excluded)</t>
-  </si>
-  <si>
-    <t>Other Adjustment</t>
-  </si>
-  <si>
-    <t>Government deduction</t>
+    <t>1760689353518111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHAFQAT ALI  MUHAMMAD AWAIS </t>
+  </si>
+  <si>
+    <t>Dubai</t>
   </si>
   <si>
     <t xml:space="preserve">valid
 </t>
   </si>
   <si>
+    <t>Nov-2025</t>
+  </si>
+  <si>
+    <t>Rider Orders Invoice Month of Nov-2025</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>If you have any discrepancies regarding this invoice, you may contact our Accounts Department within 4 days. After this period, no changes will be accepted.</t>
+  </si>
+  <si>
+    <t>1755609787580247</t>
+  </si>
+  <si>
+    <t>Muhammad Ramzan Khan Zeeshan ahmad</t>
+  </si>
+  <si>
     <t>invalid</t>
   </si>
   <si>
-    <t>Nov-2025</t>
-  </si>
-  <si>
-    <t>Rider Orders Invoice Month of Nov-2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHAFQAT ALI  MUHAMMAD AWAIS </t>
-  </si>
-  <si>
-    <t>Muhammad Ramzan Khan Zeeshan ahmad</t>
+    <t>1760347061514782</t>
   </si>
   <si>
     <t>Abdul Rusheed Usman Ghani</t>
   </si>
   <si>
+    <t>1755184078593176</t>
+  </si>
+  <si>
     <t>Abdul Hamid Laskar Miraj Laskar</t>
   </si>
   <si>
+    <t>1760703460580878</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mehmood Kashif </t>
   </si>
   <si>
+    <t>1756560292593723</t>
+  </si>
+  <si>
     <t>Noman Ali Noman Ali</t>
   </si>
   <si>
+    <t>1761214567593961</t>
+  </si>
+  <si>
     <t>Kamran Pervaiz Muhammad Pervaiz Kamran Pervaiz Muhammad Pervaiz</t>
   </si>
   <si>
+    <t>1760955450512225</t>
+  </si>
+  <si>
     <t>Shahid Munir Munir Ahmad Shahid Munir Munir Ahmad</t>
   </si>
   <si>
+    <t>1760514962580200</t>
+  </si>
+  <si>
     <t xml:space="preserve">muhammad afzal umar afzal </t>
   </si>
   <si>
+    <t>1760431981593175</t>
+  </si>
+  <si>
     <t>Nshimirimana Libere</t>
   </si>
   <si>
+    <t>1761373911514283</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sayed Alam Shahadat Hossain </t>
   </si>
   <si>
+    <t>1755069750514650</t>
+  </si>
+  <si>
     <t>Haq Nawaz Sajid Nawaz</t>
   </si>
   <si>
+    <t>1755946386518969</t>
+  </si>
+  <si>
     <t>Hamim Ullah Noaman Ullah</t>
   </si>
   <si>
+    <t>1758800285521777</t>
+  </si>
+  <si>
     <t>Abdul Ghaffar Ali Ahsan Raza</t>
   </si>
   <si>
+    <t>1760518463554643</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Muhammad Nadeem Talha Nadeem </t>
   </si>
   <si>
+    <t>1760431690518469</t>
+  </si>
+  <si>
     <t xml:space="preserve">Muhammad Munir Muhammad Saleem </t>
   </si>
   <si>
+    <t>1755074920518523</t>
+  </si>
+  <si>
     <t>Ehsan Baig Mirza Mohsin Ehsan</t>
   </si>
   <si>
+    <t>1760535067518119</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pritam Singh Gurkit Singh </t>
   </si>
   <si>
+    <t>1755577297593070</t>
+  </si>
+  <si>
     <t>Muhammad Iqbal Naveed Iqba</t>
   </si>
   <si>
+    <t>1755334775593815</t>
+  </si>
+  <si>
     <t>Muhammad Latif Shahzad Ali</t>
   </si>
   <si>
-    <t>1760689353518111</t>
-  </si>
-  <si>
-    <t>1755609787580247</t>
-  </si>
-  <si>
-    <t>1760347061514782</t>
-  </si>
-  <si>
-    <t>1755184078593176</t>
-  </si>
-  <si>
-    <t>1760703460580878</t>
-  </si>
-  <si>
-    <t>1756560292593723</t>
-  </si>
-  <si>
-    <t>1761214567593961</t>
-  </si>
-  <si>
-    <t>1760955450512225</t>
-  </si>
-  <si>
-    <t>1760514962580200</t>
-  </si>
-  <si>
-    <t>1760431981593175</t>
-  </si>
-  <si>
-    <t>1761373911514283</t>
-  </si>
-  <si>
-    <t>1755069750514650</t>
-  </si>
-  <si>
-    <t>1755946386518969</t>
-  </si>
-  <si>
-    <t>1758800285521777</t>
-  </si>
-  <si>
-    <t>1760518463554643</t>
-  </si>
-  <si>
-    <t>1760431690518469</t>
-  </si>
-  <si>
-    <t>1755074920518523</t>
-  </si>
-  <si>
-    <t>1760535067518119</t>
-  </si>
-  <si>
-    <t>1755577297593070</t>
-  </si>
-  <si>
-    <t>1755334775593815</t>
-  </si>
-  <si>
-    <t>Performance</t>
-  </si>
-  <si>
-    <t>Rejection</t>
-  </si>
-  <si>
-    <t>Login Hours</t>
-  </si>
-  <si>
-    <t>Zone</t>
-  </si>
-  <si>
-    <t>Working Days</t>
-  </si>
-  <si>
-    <t>Perf_Attendance</t>
-  </si>
-  <si>
-    <t>Off</t>
-  </si>
-  <si>
-    <t>Dubai</t>
+    <t>Government deduction</t>
+  </si>
+  <si>
+    <t>Other Adjustment</t>
+  </si>
+  <si>
+    <t>Tips(VAT Excluded)</t>
+  </si>
+  <si>
+    <t>Deduction</t>
+  </si>
+  <si>
+    <t>food compensation</t>
+  </si>
+  <si>
+    <t>Other Rewards</t>
+  </si>
+  <si>
+    <t>Flexible subsidy</t>
+  </si>
+  <si>
+    <t>Activity rewards</t>
+  </si>
+  <si>
+    <t>Attendance incentive</t>
+  </si>
+  <si>
+    <t>Guaranteed subsidy</t>
+  </si>
+  <si>
+    <t>Delivery fees</t>
+  </si>
+  <si>
+    <t>branch_id</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d/mmm/yyyy;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -288,34 +277,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="17" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="164" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="1" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -357,7 +338,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -409,7 +390,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -461,7 +442,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -470,262 +451,293 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y324"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:Z324"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="8"/>
-    <col min="11" max="11" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="37.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="true" style="0"/>
+    <col min="2" max="2" width="17.28515625" customWidth="true" style="0"/>
+    <col min="3" max="3" width="37.7109375" customWidth="true" style="0"/>
+    <col min="4" max="4" width="9.42578125" customWidth="true" style="6"/>
+    <col min="5" max="5" width="11.28515625" customWidth="true" style="6"/>
+    <col min="6" max="6" width="5.7109375" customWidth="true" style="6"/>
+    <col min="7" max="7" width="13.140625" customWidth="true" style="6"/>
+    <col min="8" max="8" width="16.140625" customWidth="true" style="0"/>
+    <col min="9" max="9" width="3.85546875" customWidth="true" style="0"/>
+    <col min="10" max="10" width="9.140625" customWidth="true" style="8"/>
+    <col min="11" max="11" width="12.85546875" customWidth="true" style="0"/>
+    <col min="12" max="12" width="37.140625" customWidth="true" style="7"/>
+    <col min="13" max="13" width="7.28515625" customWidth="true" style="0"/>
+    <col min="14" max="14" width="7.28515625" customWidth="true" style="0"/>
+    <col min="16" max="16" width="12.7109375" customWidth="true" style="0"/>
+    <col min="17" max="17" width="18.85546875" customWidth="true" style="0"/>
+    <col min="18" max="18" width="20.28515625" customWidth="true" style="0"/>
+    <col min="19" max="19" width="15.42578125" customWidth="true" style="0"/>
+    <col min="20" max="20" width="15.42578125" customWidth="true" style="0"/>
+    <col min="21" max="21" width="14.28515625" customWidth="true" style="0"/>
+    <col min="22" max="22" width="18.42578125" customWidth="true" style="0"/>
+    <col min="23" max="23" width="10.140625" customWidth="true" style="0"/>
+    <col min="24" max="24" width="18.28515625" customWidth="true" style="0"/>
+    <col min="25" max="25" width="17.28515625" customWidth="true" style="0"/>
+    <col min="26" max="26" width="22" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>72</v>
+      </c>
+      <c r="P1" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>70</v>
+      </c>
+      <c r="R1" t="s">
+        <v>69</v>
+      </c>
+      <c r="S1" t="s">
+        <v>68</v>
+      </c>
+      <c r="T1" t="s">
+        <v>67</v>
+      </c>
+      <c r="U1" t="s">
+        <v>66</v>
+      </c>
+      <c r="V1" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="J1" s="8" t="s">
+      <c r="W1" t="s">
         <v>64</v>
       </c>
-      <c r="K1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="M1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" t="s">
-        <v>5</v>
-      </c>
-      <c r="O1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>11</v>
-      </c>
-      <c r="R1" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" t="s">
-        <v>13</v>
-      </c>
-      <c r="T1" t="s">
-        <v>14</v>
-      </c>
-      <c r="U1" t="s">
-        <v>15</v>
-      </c>
-      <c r="V1" t="s">
-        <v>16</v>
-      </c>
-      <c r="W1" t="s">
-        <v>17</v>
-      </c>
       <c r="X1" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="Y1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26">
       <c r="A2" s="3">
         <v>45992</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D2" s="7">
         <v>2</v>
@@ -734,7 +746,7 @@
         <v>100</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G2" s="7">
         <v>10</v>
@@ -746,26 +758,24 @@
         <v>5</v>
       </c>
       <c r="J2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="N2" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" s="5">
+        <v>21</v>
+      </c>
+      <c r="O2"/>
+      <c r="P2" s="5">
         <v>1765</v>
       </c>
-      <c r="P2" s="5">
-        <v>0</v>
-      </c>
       <c r="Q2" s="5">
         <v>0</v>
       </c>
@@ -773,36 +783,39 @@
         <v>0</v>
       </c>
       <c r="S2" s="5">
+        <v>0</v>
+      </c>
+      <c r="T2" s="5">
         <v>660</v>
       </c>
-      <c r="T2" s="5">
-        <v>0</v>
-      </c>
       <c r="U2" s="5">
+        <v>0</v>
+      </c>
+      <c r="V2" s="5">
         <v>44.5</v>
       </c>
-      <c r="V2" s="5">
+      <c r="W2" s="5">
         <v>10.5</v>
       </c>
-      <c r="W2" s="5">
+      <c r="X2" s="5">
         <v>24</v>
       </c>
-      <c r="X2" s="5">
-        <v>0</v>
-      </c>
       <c r="Y2" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z2" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3" s="3">
         <v>45992</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" s="7">
         <v>2</v>
@@ -811,7 +824,7 @@
         <v>100</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G3" s="7">
         <v>10</v>
@@ -823,26 +836,24 @@
         <v>5</v>
       </c>
       <c r="J3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N3" t="s">
-        <v>6</v>
-      </c>
-      <c r="O3" s="5">
+      <c r="O3"/>
+      <c r="P3" s="5">
         <v>1905</v>
       </c>
-      <c r="P3" s="5">
-        <v>0</v>
-      </c>
       <c r="Q3" s="5">
         <v>0</v>
       </c>
@@ -850,11 +861,11 @@
         <v>0</v>
       </c>
       <c r="S3" s="5">
+        <v>0</v>
+      </c>
+      <c r="T3" s="5">
         <v>1023</v>
       </c>
-      <c r="T3" s="5">
-        <v>0</v>
-      </c>
       <c r="U3" s="5">
         <v>0</v>
       </c>
@@ -862,21 +873,24 @@
         <v>0</v>
       </c>
       <c r="W3" s="5">
+        <v>0</v>
+      </c>
+      <c r="X3" s="5">
         <v>16</v>
       </c>
-      <c r="X3" s="5">
+      <c r="Y3" s="5">
         <v>500</v>
       </c>
-      <c r="Y3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4" s="3">
         <v>45992</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
@@ -888,7 +902,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G4" s="7">
         <v>10</v>
@@ -900,26 +914,24 @@
         <v>5</v>
       </c>
       <c r="J4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="N4" t="s">
-        <v>6</v>
-      </c>
-      <c r="O4" s="5">
+        <v>21</v>
+      </c>
+      <c r="O4"/>
+      <c r="P4" s="5">
         <v>1709.23</v>
       </c>
-      <c r="P4" s="5">
-        <v>0</v>
-      </c>
       <c r="Q4" s="5">
         <v>0</v>
       </c>
@@ -927,36 +939,39 @@
         <v>0</v>
       </c>
       <c r="S4" s="5">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5">
         <v>956</v>
       </c>
-      <c r="T4" s="5">
-        <v>0</v>
-      </c>
       <c r="U4" s="5">
         <v>0</v>
       </c>
       <c r="V4" s="5">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5">
         <v>1.5</v>
       </c>
-      <c r="W4" s="5">
+      <c r="X4" s="5">
         <v>20</v>
       </c>
-      <c r="X4" s="5">
+      <c r="Y4" s="5">
         <v>10</v>
       </c>
-      <c r="Y4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" s="3">
         <v>45992</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="7">
         <v>2</v>
@@ -965,7 +980,7 @@
         <v>100</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G5" s="7">
         <v>10</v>
@@ -977,26 +992,24 @@
         <v>5</v>
       </c>
       <c r="J5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="N5" t="s">
-        <v>6</v>
-      </c>
-      <c r="O5" s="5">
+        <v>21</v>
+      </c>
+      <c r="O5"/>
+      <c r="P5" s="5">
         <v>190</v>
       </c>
-      <c r="P5" s="5">
-        <v>0</v>
-      </c>
       <c r="Q5" s="5">
         <v>0</v>
       </c>
@@ -1004,36 +1017,39 @@
         <v>0</v>
       </c>
       <c r="S5" s="5">
+        <v>0</v>
+      </c>
+      <c r="T5" s="5">
         <v>45</v>
       </c>
-      <c r="T5" s="5">
-        <v>0</v>
-      </c>
       <c r="U5" s="5">
         <v>0</v>
       </c>
       <c r="V5" s="5">
+        <v>0</v>
+      </c>
+      <c r="W5" s="5">
         <v>3</v>
       </c>
-      <c r="W5" s="5">
+      <c r="X5" s="5">
         <v>10</v>
       </c>
-      <c r="X5" s="5">
-        <v>0</v>
-      </c>
       <c r="Y5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" s="3">
         <v>45992</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D6" s="7">
         <v>2</v>
@@ -1042,7 +1058,7 @@
         <v>100</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G6" s="7">
         <v>10</v>
@@ -1054,26 +1070,24 @@
         <v>5</v>
       </c>
       <c r="J6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" t="s">
         <v>21</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N6" t="s">
-        <v>6</v>
-      </c>
-      <c r="O6" s="5">
+      <c r="O6"/>
+      <c r="P6" s="5">
         <v>390</v>
       </c>
-      <c r="P6" s="5">
-        <v>0</v>
-      </c>
       <c r="Q6" s="5">
         <v>0</v>
       </c>
@@ -1081,36 +1095,39 @@
         <v>0</v>
       </c>
       <c r="S6" s="5">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5">
         <v>49</v>
       </c>
-      <c r="T6" s="5">
-        <v>0</v>
-      </c>
       <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5">
         <v>36.5</v>
       </c>
-      <c r="V6" s="5">
+      <c r="W6" s="5">
         <v>15</v>
       </c>
-      <c r="W6" s="5">
-        <v>0</v>
-      </c>
       <c r="X6" s="5">
         <v>0</v>
       </c>
       <c r="Y6" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26">
       <c r="A7" s="3">
         <v>45992</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D7" s="7">
         <v>2</v>
@@ -1119,7 +1136,7 @@
         <v>100</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G7" s="7">
         <v>10</v>
@@ -1131,63 +1148,64 @@
         <v>5</v>
       </c>
       <c r="J7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="8" t="s">
+      <c r="O7"/>
+      <c r="P7" s="5">
+        <v>1596</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+      <c r="T7" s="5">
+        <v>549</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5">
+        <v>0</v>
+      </c>
+      <c r="W7" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="X7" s="5">
         <v>23</v>
       </c>
-      <c r="M7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N7" t="s">
-        <v>6</v>
-      </c>
-      <c r="O7" s="5">
-        <v>1596</v>
-      </c>
-      <c r="P7" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="5">
-        <v>0</v>
-      </c>
-      <c r="R7" s="5">
-        <v>0</v>
-      </c>
-      <c r="S7" s="5">
-        <v>549</v>
-      </c>
-      <c r="T7" s="5">
-        <v>0</v>
-      </c>
-      <c r="U7" s="5">
-        <v>0</v>
-      </c>
-      <c r="V7" s="5">
-        <v>4.5</v>
-      </c>
-      <c r="W7" s="5">
-        <v>23</v>
-      </c>
-      <c r="X7" s="5">
-        <v>0</v>
-      </c>
       <c r="Y7" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26">
       <c r="A8" s="3">
         <v>45992</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D8" s="7">
         <v>2</v>
@@ -1196,7 +1214,7 @@
         <v>100</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G8" s="7">
         <v>10</v>
@@ -1208,26 +1226,24 @@
         <v>5</v>
       </c>
       <c r="J8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N8" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" t="s">
-        <v>6</v>
-      </c>
-      <c r="O8" s="5">
+      <c r="O8"/>
+      <c r="P8" s="5">
         <v>1045</v>
       </c>
-      <c r="P8" s="5">
-        <v>0</v>
-      </c>
       <c r="Q8" s="5">
         <v>0</v>
       </c>
@@ -1235,36 +1251,39 @@
         <v>0</v>
       </c>
       <c r="S8" s="5">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5">
         <v>75</v>
       </c>
-      <c r="T8" s="5">
-        <v>0</v>
-      </c>
       <c r="U8" s="5">
         <v>0</v>
       </c>
       <c r="V8" s="5">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5">
         <v>1.5</v>
       </c>
-      <c r="W8" s="5">
+      <c r="X8" s="5">
         <v>14</v>
       </c>
-      <c r="X8" s="5">
-        <v>0</v>
-      </c>
       <c r="Y8" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26">
       <c r="A9" s="3">
         <v>45992</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D9" s="7">
         <v>2</v>
@@ -1273,7 +1292,7 @@
         <v>100</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G9" s="7">
         <v>10</v>
@@ -1285,26 +1304,24 @@
         <v>5</v>
       </c>
       <c r="J9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="N9" t="s">
-        <v>6</v>
-      </c>
-      <c r="O9" s="5">
+        <v>21</v>
+      </c>
+      <c r="O9"/>
+      <c r="P9" s="5">
         <v>2625</v>
       </c>
-      <c r="P9" s="5">
-        <v>0</v>
-      </c>
       <c r="Q9" s="5">
         <v>0</v>
       </c>
@@ -1312,36 +1329,39 @@
         <v>0</v>
       </c>
       <c r="S9" s="5">
+        <v>0</v>
+      </c>
+      <c r="T9" s="5">
         <v>1256</v>
       </c>
-      <c r="T9" s="5">
-        <v>0</v>
-      </c>
       <c r="U9" s="5">
         <v>0</v>
       </c>
       <c r="V9" s="5">
+        <v>0</v>
+      </c>
+      <c r="W9" s="5">
         <v>1.5</v>
       </c>
-      <c r="W9" s="5">
+      <c r="X9" s="5">
         <v>30</v>
       </c>
-      <c r="X9" s="5">
+      <c r="Y9" s="5">
         <v>500</v>
       </c>
-      <c r="Y9" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26">
       <c r="A10" s="3">
         <v>45992</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D10" s="7">
         <v>2</v>
@@ -1350,7 +1370,7 @@
         <v>100</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G10" s="7">
         <v>10</v>
@@ -1362,26 +1382,24 @@
         <v>5</v>
       </c>
       <c r="J10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" t="s">
         <v>21</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" t="s">
-        <v>6</v>
-      </c>
-      <c r="O10" s="5">
+      <c r="O10"/>
+      <c r="P10" s="5">
         <v>2150</v>
       </c>
-      <c r="P10" s="5">
-        <v>0</v>
-      </c>
       <c r="Q10" s="5">
         <v>0</v>
       </c>
@@ -1389,36 +1407,39 @@
         <v>0</v>
       </c>
       <c r="S10" s="5">
+        <v>0</v>
+      </c>
+      <c r="T10" s="5">
         <v>835</v>
       </c>
-      <c r="T10" s="5">
-        <v>0</v>
-      </c>
       <c r="U10" s="5">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5">
         <v>39</v>
       </c>
-      <c r="V10" s="5">
+      <c r="W10" s="5">
         <v>12</v>
       </c>
-      <c r="W10" s="5">
+      <c r="X10" s="5">
         <v>32</v>
       </c>
-      <c r="X10" s="5">
+      <c r="Y10" s="5">
         <v>510</v>
       </c>
-      <c r="Y10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26">
       <c r="A11" s="3">
         <v>45992</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D11" s="7">
         <v>2</v>
@@ -1427,7 +1448,7 @@
         <v>100</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G11" s="7">
         <v>10</v>
@@ -1439,26 +1460,24 @@
         <v>5</v>
       </c>
       <c r="J11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="N11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O11" s="5">
+        <v>21</v>
+      </c>
+      <c r="O11"/>
+      <c r="P11" s="5">
         <v>2615</v>
       </c>
-      <c r="P11" s="5">
-        <v>0</v>
-      </c>
       <c r="Q11" s="5">
         <v>0</v>
       </c>
@@ -1466,36 +1485,39 @@
         <v>0</v>
       </c>
       <c r="S11" s="5">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5">
         <v>780</v>
       </c>
-      <c r="T11" s="5">
-        <v>0</v>
-      </c>
       <c r="U11" s="5">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5">
         <v>26.6</v>
       </c>
-      <c r="V11" s="5">
+      <c r="W11" s="5">
         <v>19.5</v>
       </c>
-      <c r="W11" s="5">
+      <c r="X11" s="5">
         <v>19</v>
       </c>
-      <c r="X11" s="5">
+      <c r="Y11" s="5">
         <v>10</v>
       </c>
-      <c r="Y11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
       <c r="A12" s="3">
         <v>45992</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D12" s="7">
         <v>2</v>
@@ -1504,7 +1526,7 @@
         <v>100</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G12" s="7">
         <v>10</v>
@@ -1516,26 +1538,24 @@
         <v>5</v>
       </c>
       <c r="J12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N12" t="s">
         <v>21</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N12" t="s">
-        <v>6</v>
-      </c>
-      <c r="O12" s="5">
+      <c r="O12"/>
+      <c r="P12" s="5">
         <v>40</v>
       </c>
-      <c r="P12" s="5">
-        <v>0</v>
-      </c>
       <c r="Q12" s="5">
         <v>0</v>
       </c>
@@ -1543,11 +1563,11 @@
         <v>0</v>
       </c>
       <c r="S12" s="5">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5">
         <v>4</v>
       </c>
-      <c r="T12" s="5">
-        <v>0</v>
-      </c>
       <c r="U12" s="5">
         <v>0</v>
       </c>
@@ -1563,16 +1583,19 @@
       <c r="Y12" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
       <c r="A13" s="3">
         <v>45992</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D13" s="7">
         <v>2</v>
@@ -1581,7 +1604,7 @@
         <v>100</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G13" s="7">
         <v>10</v>
@@ -1593,26 +1616,24 @@
         <v>5</v>
       </c>
       <c r="J13" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="N13" t="s">
-        <v>6</v>
-      </c>
-      <c r="O13" s="5">
+        <v>21</v>
+      </c>
+      <c r="O13"/>
+      <c r="P13" s="5">
         <v>1790</v>
       </c>
-      <c r="P13" s="5">
-        <v>0</v>
-      </c>
       <c r="Q13" s="5">
         <v>0</v>
       </c>
@@ -1620,11 +1641,11 @@
         <v>0</v>
       </c>
       <c r="S13" s="5">
+        <v>0</v>
+      </c>
+      <c r="T13" s="5">
         <v>899</v>
       </c>
-      <c r="T13" s="5">
-        <v>0</v>
-      </c>
       <c r="U13" s="5">
         <v>0</v>
       </c>
@@ -1632,24 +1653,27 @@
         <v>0</v>
       </c>
       <c r="W13" s="5">
+        <v>0</v>
+      </c>
+      <c r="X13" s="5">
         <v>14</v>
       </c>
-      <c r="X13" s="5">
+      <c r="Y13" s="5">
         <v>520</v>
       </c>
-      <c r="Y13" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26">
       <c r="A14" s="3">
         <v>45992</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D14" s="7">
         <v>2</v>
@@ -1658,7 +1682,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G14" s="7">
         <v>10</v>
@@ -1670,26 +1694,24 @@
         <v>5</v>
       </c>
       <c r="J14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N14" t="s">
         <v>21</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" t="s">
-        <v>6</v>
-      </c>
-      <c r="O14" s="5">
+      <c r="O14"/>
+      <c r="P14" s="5">
         <v>1713.46</v>
       </c>
-      <c r="P14" s="5">
-        <v>0</v>
-      </c>
       <c r="Q14" s="5">
         <v>0</v>
       </c>
@@ -1697,11 +1719,11 @@
         <v>0</v>
       </c>
       <c r="S14" s="5">
+        <v>0</v>
+      </c>
+      <c r="T14" s="5">
         <v>607</v>
       </c>
-      <c r="T14" s="5">
-        <v>0</v>
-      </c>
       <c r="U14" s="5">
         <v>0</v>
       </c>
@@ -1709,24 +1731,27 @@
         <v>0</v>
       </c>
       <c r="W14" s="5">
+        <v>0</v>
+      </c>
+      <c r="X14" s="5">
         <v>41</v>
       </c>
-      <c r="X14" s="5">
+      <c r="Y14" s="5">
         <v>515</v>
       </c>
-      <c r="Y14" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26">
       <c r="A15" s="3">
         <v>45992</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D15" s="7">
         <v>2</v>
@@ -1735,7 +1760,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G15" s="7">
         <v>10</v>
@@ -1747,26 +1772,24 @@
         <v>5</v>
       </c>
       <c r="J15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="N15" t="s">
-        <v>6</v>
-      </c>
-      <c r="O15" s="5">
+        <v>21</v>
+      </c>
+      <c r="O15"/>
+      <c r="P15" s="5">
         <v>5348</v>
       </c>
-      <c r="P15" s="5">
-        <v>0</v>
-      </c>
       <c r="Q15" s="5">
         <v>0</v>
       </c>
@@ -1774,36 +1797,39 @@
         <v>0</v>
       </c>
       <c r="S15" s="5">
+        <v>0</v>
+      </c>
+      <c r="T15" s="5">
         <v>1088</v>
       </c>
-      <c r="T15" s="5">
-        <v>0</v>
-      </c>
       <c r="U15" s="5">
+        <v>0</v>
+      </c>
+      <c r="V15" s="5">
         <v>33.5</v>
       </c>
-      <c r="V15" s="5">
+      <c r="W15" s="5">
         <v>15.5</v>
       </c>
-      <c r="W15" s="5">
+      <c r="X15" s="5">
         <v>13</v>
       </c>
-      <c r="X15" s="5">
-        <v>0</v>
-      </c>
       <c r="Y15" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26">
       <c r="A16" s="3">
         <v>45992</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D16" s="7">
         <v>2</v>
@@ -1812,7 +1838,7 @@
         <v>100</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G16" s="7">
         <v>10</v>
@@ -1824,26 +1850,24 @@
         <v>5</v>
       </c>
       <c r="J16" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="N16" t="s">
-        <v>6</v>
-      </c>
-      <c r="O16" s="5">
+        <v>21</v>
+      </c>
+      <c r="O16"/>
+      <c r="P16" s="5">
         <v>2215</v>
       </c>
-      <c r="P16" s="5">
-        <v>0</v>
-      </c>
       <c r="Q16" s="5">
         <v>0</v>
       </c>
@@ -1851,36 +1875,39 @@
         <v>0</v>
       </c>
       <c r="S16" s="5">
+        <v>0</v>
+      </c>
+      <c r="T16" s="5">
         <v>720</v>
       </c>
-      <c r="T16" s="5">
-        <v>0</v>
-      </c>
       <c r="U16" s="5">
         <v>0</v>
       </c>
       <c r="V16" s="5">
+        <v>0</v>
+      </c>
+      <c r="W16" s="5">
         <v>1.5</v>
       </c>
-      <c r="W16" s="5">
+      <c r="X16" s="5">
         <v>25</v>
       </c>
-      <c r="X16" s="5">
+      <c r="Y16" s="5">
         <v>30</v>
       </c>
-      <c r="Y16" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26">
       <c r="A17" s="3">
         <v>45992</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D17" s="7">
         <v>2</v>
@@ -1889,7 +1916,7 @@
         <v>100</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G17" s="7">
         <v>10</v>
@@ -1901,63 +1928,64 @@
         <v>5</v>
       </c>
       <c r="J17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N17" t="s">
         <v>21</v>
       </c>
-      <c r="K17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" t="s">
+      <c r="O17"/>
+      <c r="P17" s="5">
+        <v>1745</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>0</v>
+      </c>
+      <c r="R17" s="5">
+        <v>0</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
+      <c r="T17" s="5">
+        <v>999</v>
+      </c>
+      <c r="U17" s="5">
+        <v>0</v>
+      </c>
+      <c r="V17" s="5">
+        <v>0</v>
+      </c>
+      <c r="W17" s="5">
         <v>6</v>
       </c>
-      <c r="O17" s="5">
-        <v>1745</v>
-      </c>
-      <c r="P17" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="5">
-        <v>0</v>
-      </c>
-      <c r="R17" s="5">
-        <v>0</v>
-      </c>
-      <c r="S17" s="5">
-        <v>999</v>
-      </c>
-      <c r="T17" s="5">
-        <v>0</v>
-      </c>
-      <c r="U17" s="5">
-        <v>0</v>
-      </c>
-      <c r="V17" s="5">
-        <v>6</v>
-      </c>
-      <c r="W17" s="5">
+      <c r="X17" s="5">
         <v>18</v>
       </c>
-      <c r="X17" s="5">
+      <c r="Y17" s="5">
         <v>15</v>
       </c>
-      <c r="Y17" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
       <c r="A18" s="3">
         <v>45992</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D18" s="7">
         <v>2</v>
@@ -1966,7 +1994,7 @@
         <v>100</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G18" s="7">
         <v>10</v>
@@ -1978,63 +2006,64 @@
         <v>5</v>
       </c>
       <c r="J18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N18" t="s">
         <v>21</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" t="s">
-        <v>6</v>
-      </c>
-      <c r="O18" s="5">
+      <c r="O18"/>
+      <c r="P18" s="5">
         <v>4681</v>
       </c>
-      <c r="P18" s="5">
-        <v>0</v>
-      </c>
       <c r="Q18" s="5">
         <v>0</v>
       </c>
       <c r="R18" s="5">
+        <v>0</v>
+      </c>
+      <c r="S18" s="5">
         <v>200</v>
       </c>
-      <c r="S18" s="5">
+      <c r="T18" s="5">
         <v>2163</v>
       </c>
-      <c r="T18" s="5">
-        <v>0</v>
-      </c>
       <c r="U18" s="5">
+        <v>0</v>
+      </c>
+      <c r="V18" s="5">
         <v>29.4</v>
       </c>
-      <c r="V18" s="5">
+      <c r="W18" s="5">
         <v>12</v>
       </c>
-      <c r="W18" s="5">
+      <c r="X18" s="5">
         <v>36</v>
       </c>
-      <c r="X18" s="5">
+      <c r="Y18" s="5">
         <v>400</v>
       </c>
-      <c r="Y18" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26">
       <c r="A19" s="3">
         <v>45992</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D19" s="7">
         <v>2</v>
@@ -2043,7 +2072,7 @@
         <v>100</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G19" s="7">
         <v>10</v>
@@ -2055,26 +2084,24 @@
         <v>5</v>
       </c>
       <c r="J19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N19" t="s">
         <v>21</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N19" t="s">
-        <v>6</v>
-      </c>
-      <c r="O19" s="5">
+      <c r="O19"/>
+      <c r="P19" s="5">
         <v>995</v>
       </c>
-      <c r="P19" s="5">
-        <v>0</v>
-      </c>
       <c r="Q19" s="5">
         <v>0</v>
       </c>
@@ -2082,36 +2109,39 @@
         <v>0</v>
       </c>
       <c r="S19" s="5">
+        <v>0</v>
+      </c>
+      <c r="T19" s="5">
         <v>181</v>
       </c>
-      <c r="T19" s="5">
-        <v>0</v>
-      </c>
       <c r="U19" s="5">
         <v>0</v>
       </c>
       <c r="V19" s="5">
+        <v>0</v>
+      </c>
+      <c r="W19" s="5">
         <v>1.5</v>
       </c>
-      <c r="W19" s="5">
+      <c r="X19" s="5">
         <v>10</v>
       </c>
-      <c r="X19" s="5">
-        <v>0</v>
-      </c>
       <c r="Y19" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z19" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26">
       <c r="A20" s="3">
         <v>45992</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D20" s="7">
         <v>2</v>
@@ -2120,7 +2150,7 @@
         <v>100</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G20" s="7">
         <v>10</v>
@@ -2132,26 +2162,24 @@
         <v>5</v>
       </c>
       <c r="J20" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M20" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="N20" t="s">
-        <v>6</v>
-      </c>
-      <c r="O20" s="5">
+        <v>21</v>
+      </c>
+      <c r="O20"/>
+      <c r="P20" s="5">
         <v>1895</v>
       </c>
-      <c r="P20" s="5">
-        <v>0</v>
-      </c>
       <c r="Q20" s="5">
         <v>0</v>
       </c>
@@ -2159,36 +2187,39 @@
         <v>0</v>
       </c>
       <c r="S20" s="5">
+        <v>0</v>
+      </c>
+      <c r="T20" s="5">
         <v>701</v>
       </c>
-      <c r="T20" s="5">
-        <v>0</v>
-      </c>
       <c r="U20" s="5">
         <v>0</v>
       </c>
       <c r="V20" s="5">
+        <v>0</v>
+      </c>
+      <c r="W20" s="5">
         <v>9</v>
       </c>
-      <c r="W20" s="5">
+      <c r="X20" s="5">
         <v>15</v>
       </c>
-      <c r="X20" s="5">
+      <c r="Y20" s="5">
         <v>520</v>
       </c>
-      <c r="Y20" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z20" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26">
       <c r="A21" s="3">
         <v>45992</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D21" s="7">
         <v>2</v>
@@ -2197,7 +2228,7 @@
         <v>100</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="G21" s="7">
         <v>10</v>
@@ -2209,26 +2240,24 @@
         <v>5</v>
       </c>
       <c r="J21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N21" t="s">
         <v>21</v>
       </c>
-      <c r="K21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="N21" t="s">
-        <v>6</v>
-      </c>
-      <c r="O21" s="5">
+      <c r="O21"/>
+      <c r="P21" s="5">
         <v>2185</v>
       </c>
-      <c r="P21" s="5">
-        <v>0</v>
-      </c>
       <c r="Q21" s="5">
         <v>0</v>
       </c>
@@ -2236,28 +2265,31 @@
         <v>0</v>
       </c>
       <c r="S21" s="5">
+        <v>0</v>
+      </c>
+      <c r="T21" s="5">
         <v>417</v>
       </c>
-      <c r="T21" s="5">
-        <v>0</v>
-      </c>
       <c r="U21" s="5">
         <v>0</v>
       </c>
       <c r="V21" s="5">
+        <v>0</v>
+      </c>
+      <c r="W21" s="5">
         <v>1.5</v>
       </c>
-      <c r="W21" s="5">
+      <c r="X21" s="5">
         <v>12</v>
       </c>
-      <c r="X21" s="5">
-        <v>0</v>
-      </c>
       <c r="Y21" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="Z21" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26">
       <c r="A22" s="3"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -2269,8 +2301,10 @@
       <c r="L22" s="8"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="O22" s="4"/>
+      <c r="Z22"/>
+    </row>
+    <row r="23" spans="1:26">
       <c r="A23" s="3"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
@@ -2282,8 +2316,10 @@
       <c r="L23" s="8"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="O23" s="4"/>
+      <c r="Z23"/>
+    </row>
+    <row r="24" spans="1:26">
       <c r="A24" s="3"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
@@ -2295,8 +2331,10 @@
       <c r="L24" s="8"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="O24" s="4"/>
+      <c r="Z24"/>
+    </row>
+    <row r="25" spans="1:26">
       <c r="A25" s="3"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -2308,8 +2346,10 @@
       <c r="L25" s="8"/>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="O25" s="4"/>
+      <c r="Z25"/>
+    </row>
+    <row r="26" spans="1:26">
       <c r="A26" s="3"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -2321,8 +2361,10 @@
       <c r="L26" s="8"/>
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="O26" s="4"/>
+      <c r="Z26"/>
+    </row>
+    <row r="27" spans="1:26">
       <c r="A27" s="3"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -2334,8 +2376,10 @@
       <c r="L27" s="8"/>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="O27" s="4"/>
+      <c r="Z27"/>
+    </row>
+    <row r="28" spans="1:26">
       <c r="A28" s="3"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -2347,8 +2391,10 @@
       <c r="L28" s="8"/>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="O28" s="4"/>
+      <c r="Z28"/>
+    </row>
+    <row r="29" spans="1:26">
       <c r="A29" s="3"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
@@ -2360,8 +2406,10 @@
       <c r="L29" s="8"/>
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="O29" s="4"/>
+      <c r="Z29"/>
+    </row>
+    <row r="30" spans="1:26">
       <c r="A30" s="3"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -2373,8 +2421,10 @@
       <c r="L30" s="8"/>
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="O30" s="4"/>
+      <c r="Z30"/>
+    </row>
+    <row r="31" spans="1:26">
       <c r="A31" s="3"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -2386,8 +2436,10 @@
       <c r="L31" s="8"/>
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="O31" s="4"/>
+      <c r="Z31"/>
+    </row>
+    <row r="32" spans="1:26">
       <c r="A32" s="3"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -2399,8 +2451,10 @@
       <c r="L32" s="8"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O32" s="4"/>
+      <c r="Z32"/>
+    </row>
+    <row r="33" spans="1:26">
       <c r="A33" s="3"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
@@ -2412,8 +2466,10 @@
       <c r="L33" s="8"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O33" s="4"/>
+      <c r="Z33"/>
+    </row>
+    <row r="34" spans="1:26">
       <c r="A34" s="3"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -2425,8 +2481,10 @@
       <c r="L34" s="8"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O34" s="4"/>
+      <c r="Z34"/>
+    </row>
+    <row r="35" spans="1:26">
       <c r="A35" s="3"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -2438,8 +2496,10 @@
       <c r="L35" s="8"/>
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O35" s="4"/>
+      <c r="Z35"/>
+    </row>
+    <row r="36" spans="1:26">
       <c r="A36" s="3"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -2451,8 +2511,10 @@
       <c r="L36" s="8"/>
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O36" s="4"/>
+      <c r="Z36"/>
+    </row>
+    <row r="37" spans="1:26">
       <c r="A37" s="3"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -2464,8 +2526,10 @@
       <c r="L37" s="8"/>
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O37" s="4"/>
+      <c r="Z37"/>
+    </row>
+    <row r="38" spans="1:26">
       <c r="A38" s="3"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -2477,8 +2541,10 @@
       <c r="L38" s="8"/>
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O38" s="4"/>
+      <c r="Z38"/>
+    </row>
+    <row r="39" spans="1:26">
       <c r="A39" s="3"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -2490,8 +2556,10 @@
       <c r="L39" s="8"/>
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O39" s="4"/>
+      <c r="Z39"/>
+    </row>
+    <row r="40" spans="1:26">
       <c r="A40" s="3"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
@@ -2503,8 +2571,10 @@
       <c r="L40" s="8"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O40" s="4"/>
+      <c r="Z40"/>
+    </row>
+    <row r="41" spans="1:26">
       <c r="A41" s="3"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
@@ -2516,8 +2586,10 @@
       <c r="L41" s="8"/>
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O41" s="4"/>
+      <c r="Z41"/>
+    </row>
+    <row r="42" spans="1:26">
       <c r="A42" s="3"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -2529,8 +2601,10 @@
       <c r="L42" s="8"/>
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O42" s="4"/>
+      <c r="Z42"/>
+    </row>
+    <row r="43" spans="1:26">
       <c r="A43" s="3"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
@@ -2542,8 +2616,10 @@
       <c r="L43" s="8"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O43" s="4"/>
+      <c r="Z43"/>
+    </row>
+    <row r="44" spans="1:26">
       <c r="A44" s="3"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
@@ -2555,8 +2631,10 @@
       <c r="L44" s="8"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O44" s="4"/>
+      <c r="Z44"/>
+    </row>
+    <row r="45" spans="1:26">
       <c r="A45" s="3"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -2568,8 +2646,10 @@
       <c r="L45" s="8"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O45" s="4"/>
+      <c r="Z45"/>
+    </row>
+    <row r="46" spans="1:26">
       <c r="A46" s="3"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
@@ -2581,8 +2661,10 @@
       <c r="L46" s="8"/>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O46" s="4"/>
+      <c r="Z46"/>
+    </row>
+    <row r="47" spans="1:26">
       <c r="A47" s="3"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
@@ -2594,8 +2676,10 @@
       <c r="L47" s="8"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O47" s="4"/>
+      <c r="Z47"/>
+    </row>
+    <row r="48" spans="1:26">
       <c r="A48" s="3"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
@@ -2607,8 +2691,10 @@
       <c r="L48" s="8"/>
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O48" s="4"/>
+      <c r="Z48"/>
+    </row>
+    <row r="49" spans="1:26">
       <c r="A49" s="3"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
@@ -2620,8 +2706,10 @@
       <c r="L49" s="8"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O49" s="4"/>
+      <c r="Z49"/>
+    </row>
+    <row r="50" spans="1:26">
       <c r="A50" s="3"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
@@ -2633,8 +2721,10 @@
       <c r="L50" s="8"/>
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O50" s="4"/>
+      <c r="Z50"/>
+    </row>
+    <row r="51" spans="1:26">
       <c r="A51" s="3"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
@@ -2646,8 +2736,10 @@
       <c r="L51" s="8"/>
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O51" s="4"/>
+      <c r="Z51"/>
+    </row>
+    <row r="52" spans="1:26">
       <c r="A52" s="3"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
@@ -2659,8 +2751,10 @@
       <c r="L52" s="8"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O52" s="4"/>
+      <c r="Z52"/>
+    </row>
+    <row r="53" spans="1:26">
       <c r="A53" s="3"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
@@ -2672,8 +2766,10 @@
       <c r="L53" s="8"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O53" s="4"/>
+      <c r="Z53"/>
+    </row>
+    <row r="54" spans="1:26">
       <c r="A54" s="3"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
@@ -2685,8 +2781,10 @@
       <c r="L54" s="8"/>
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O54" s="4"/>
+      <c r="Z54"/>
+    </row>
+    <row r="55" spans="1:26">
       <c r="A55" s="3"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
@@ -2698,8 +2796,10 @@
       <c r="L55" s="8"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O55" s="4"/>
+      <c r="Z55"/>
+    </row>
+    <row r="56" spans="1:26">
       <c r="A56" s="3"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
@@ -2711,8 +2811,10 @@
       <c r="L56" s="8"/>
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O56" s="4"/>
+      <c r="Z56"/>
+    </row>
+    <row r="57" spans="1:26">
       <c r="A57" s="3"/>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
@@ -2724,8 +2826,10 @@
       <c r="L57" s="8"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O57" s="4"/>
+      <c r="Z57"/>
+    </row>
+    <row r="58" spans="1:26">
       <c r="A58" s="3"/>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
@@ -2737,8 +2841,10 @@
       <c r="L58" s="8"/>
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O58" s="4"/>
+      <c r="Z58"/>
+    </row>
+    <row r="59" spans="1:26">
       <c r="A59" s="3"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
@@ -2750,8 +2856,10 @@
       <c r="L59" s="8"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O59" s="4"/>
+      <c r="Z59"/>
+    </row>
+    <row r="60" spans="1:26">
       <c r="A60" s="3"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
@@ -2763,8 +2871,10 @@
       <c r="L60" s="8"/>
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O60" s="4"/>
+      <c r="Z60"/>
+    </row>
+    <row r="61" spans="1:26">
       <c r="A61" s="3"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
@@ -2776,8 +2886,10 @@
       <c r="L61" s="8"/>
       <c r="M61" s="4"/>
       <c r="N61" s="4"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O61" s="4"/>
+      <c r="Z61"/>
+    </row>
+    <row r="62" spans="1:26">
       <c r="A62" s="3"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
@@ -2789,8 +2901,10 @@
       <c r="L62" s="8"/>
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O62" s="4"/>
+      <c r="Z62"/>
+    </row>
+    <row r="63" spans="1:26">
       <c r="A63" s="3"/>
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
@@ -2802,8 +2916,10 @@
       <c r="L63" s="8"/>
       <c r="M63" s="4"/>
       <c r="N63" s="4"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O63" s="4"/>
+      <c r="Z63"/>
+    </row>
+    <row r="64" spans="1:26">
       <c r="A64" s="3"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
@@ -2815,8 +2931,10 @@
       <c r="L64" s="8"/>
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O64" s="4"/>
+      <c r="Z64"/>
+    </row>
+    <row r="65" spans="1:26">
       <c r="A65" s="3"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
@@ -2828,8 +2946,10 @@
       <c r="L65" s="8"/>
       <c r="M65" s="4"/>
       <c r="N65" s="4"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O65" s="4"/>
+      <c r="Z65"/>
+    </row>
+    <row r="66" spans="1:26">
       <c r="A66" s="3"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7"/>
@@ -2841,8 +2961,10 @@
       <c r="L66" s="8"/>
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O66" s="4"/>
+      <c r="Z66"/>
+    </row>
+    <row r="67" spans="1:26">
       <c r="A67" s="3"/>
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
@@ -2854,8 +2976,10 @@
       <c r="L67" s="8"/>
       <c r="M67" s="4"/>
       <c r="N67" s="4"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O67" s="4"/>
+      <c r="Z67"/>
+    </row>
+    <row r="68" spans="1:26">
       <c r="A68" s="3"/>
       <c r="D68" s="7"/>
       <c r="E68" s="7"/>
@@ -2867,8 +2991,10 @@
       <c r="L68" s="8"/>
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O68" s="4"/>
+      <c r="Z68"/>
+    </row>
+    <row r="69" spans="1:26">
       <c r="A69" s="3"/>
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
@@ -2880,8 +3006,10 @@
       <c r="L69" s="8"/>
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O69" s="4"/>
+      <c r="Z69"/>
+    </row>
+    <row r="70" spans="1:26">
       <c r="A70" s="3"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7"/>
@@ -2893,8 +3021,10 @@
       <c r="L70" s="8"/>
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O70" s="4"/>
+      <c r="Z70"/>
+    </row>
+    <row r="71" spans="1:26">
       <c r="A71" s="3"/>
       <c r="D71" s="7"/>
       <c r="E71" s="7"/>
@@ -2906,8 +3036,10 @@
       <c r="L71" s="8"/>
       <c r="M71" s="4"/>
       <c r="N71" s="4"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O71" s="4"/>
+      <c r="Z71"/>
+    </row>
+    <row r="72" spans="1:26">
       <c r="A72" s="3"/>
       <c r="D72" s="7"/>
       <c r="E72" s="7"/>
@@ -2919,8 +3051,10 @@
       <c r="L72" s="8"/>
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O72" s="4"/>
+      <c r="Z72"/>
+    </row>
+    <row r="73" spans="1:26">
       <c r="A73" s="3"/>
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
@@ -2932,8 +3066,10 @@
       <c r="L73" s="8"/>
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O73" s="4"/>
+      <c r="Z73"/>
+    </row>
+    <row r="74" spans="1:26">
       <c r="A74" s="3"/>
       <c r="D74" s="7"/>
       <c r="E74" s="7"/>
@@ -2945,8 +3081,10 @@
       <c r="L74" s="8"/>
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O74" s="4"/>
+      <c r="Z74"/>
+    </row>
+    <row r="75" spans="1:26">
       <c r="A75" s="3"/>
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
@@ -2958,8 +3096,10 @@
       <c r="L75" s="8"/>
       <c r="M75" s="4"/>
       <c r="N75" s="4"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O75" s="4"/>
+      <c r="Z75"/>
+    </row>
+    <row r="76" spans="1:26">
       <c r="A76" s="3"/>
       <c r="D76" s="7"/>
       <c r="E76" s="7"/>
@@ -2971,8 +3111,10 @@
       <c r="L76" s="8"/>
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O76" s="4"/>
+      <c r="Z76"/>
+    </row>
+    <row r="77" spans="1:26">
       <c r="A77" s="3"/>
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
@@ -2984,8 +3126,10 @@
       <c r="L77" s="8"/>
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O77" s="4"/>
+      <c r="Z77"/>
+    </row>
+    <row r="78" spans="1:26">
       <c r="A78" s="3"/>
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
@@ -2997,8 +3141,10 @@
       <c r="L78" s="8"/>
       <c r="M78" s="4"/>
       <c r="N78" s="4"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O78" s="4"/>
+      <c r="Z78"/>
+    </row>
+    <row r="79" spans="1:26">
       <c r="A79" s="3"/>
       <c r="D79" s="7"/>
       <c r="E79" s="7"/>
@@ -3010,8 +3156,10 @@
       <c r="L79" s="8"/>
       <c r="M79" s="4"/>
       <c r="N79" s="4"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O79" s="4"/>
+      <c r="Z79"/>
+    </row>
+    <row r="80" spans="1:26">
       <c r="A80" s="3"/>
       <c r="D80" s="7"/>
       <c r="E80" s="7"/>
@@ -3023,8 +3171,10 @@
       <c r="L80" s="8"/>
       <c r="M80" s="4"/>
       <c r="N80" s="4"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O80" s="4"/>
+      <c r="Z80"/>
+    </row>
+    <row r="81" spans="1:26">
       <c r="A81" s="3"/>
       <c r="D81" s="7"/>
       <c r="E81" s="7"/>
@@ -3036,8 +3186,10 @@
       <c r="L81" s="8"/>
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O81" s="4"/>
+      <c r="Z81"/>
+    </row>
+    <row r="82" spans="1:26">
       <c r="A82" s="3"/>
       <c r="D82" s="7"/>
       <c r="E82" s="7"/>
@@ -3049,8 +3201,10 @@
       <c r="L82" s="8"/>
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O82" s="4"/>
+      <c r="Z82"/>
+    </row>
+    <row r="83" spans="1:26">
       <c r="A83" s="3"/>
       <c r="D83" s="7"/>
       <c r="E83" s="7"/>
@@ -3062,8 +3216,10 @@
       <c r="L83" s="8"/>
       <c r="M83" s="4"/>
       <c r="N83" s="4"/>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O83" s="4"/>
+      <c r="Z83"/>
+    </row>
+    <row r="84" spans="1:26">
       <c r="A84" s="3"/>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
@@ -3075,8 +3231,10 @@
       <c r="L84" s="8"/>
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O84" s="4"/>
+      <c r="Z84"/>
+    </row>
+    <row r="85" spans="1:26">
       <c r="A85" s="3"/>
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
@@ -3088,8 +3246,10 @@
       <c r="L85" s="8"/>
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O85" s="4"/>
+      <c r="Z85"/>
+    </row>
+    <row r="86" spans="1:26">
       <c r="A86" s="3"/>
       <c r="D86" s="7"/>
       <c r="E86" s="7"/>
@@ -3101,8 +3261,10 @@
       <c r="L86" s="8"/>
       <c r="M86" s="4"/>
       <c r="N86" s="4"/>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O86" s="4"/>
+      <c r="Z86"/>
+    </row>
+    <row r="87" spans="1:26">
       <c r="A87" s="3"/>
       <c r="D87" s="7"/>
       <c r="E87" s="7"/>
@@ -3114,8 +3276,10 @@
       <c r="L87" s="8"/>
       <c r="M87" s="4"/>
       <c r="N87" s="4"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O87" s="4"/>
+      <c r="Z87"/>
+    </row>
+    <row r="88" spans="1:26">
       <c r="A88" s="3"/>
       <c r="D88" s="7"/>
       <c r="E88" s="7"/>
@@ -3127,8 +3291,10 @@
       <c r="L88" s="8"/>
       <c r="M88" s="4"/>
       <c r="N88" s="4"/>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O88" s="4"/>
+      <c r="Z88"/>
+    </row>
+    <row r="89" spans="1:26">
       <c r="A89" s="3"/>
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
@@ -3140,8 +3306,10 @@
       <c r="L89" s="8"/>
       <c r="M89" s="4"/>
       <c r="N89" s="4"/>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O89" s="4"/>
+      <c r="Z89"/>
+    </row>
+    <row r="90" spans="1:26">
       <c r="A90" s="3"/>
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
@@ -3153,8 +3321,10 @@
       <c r="L90" s="8"/>
       <c r="M90" s="4"/>
       <c r="N90" s="4"/>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O90" s="4"/>
+      <c r="Z90"/>
+    </row>
+    <row r="91" spans="1:26">
       <c r="A91" s="3"/>
       <c r="D91" s="7"/>
       <c r="E91" s="7"/>
@@ -3166,8 +3336,10 @@
       <c r="L91" s="8"/>
       <c r="M91" s="4"/>
       <c r="N91" s="4"/>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O91" s="4"/>
+      <c r="Z91"/>
+    </row>
+    <row r="92" spans="1:26">
       <c r="A92" s="3"/>
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
@@ -3179,8 +3351,10 @@
       <c r="L92" s="8"/>
       <c r="M92" s="4"/>
       <c r="N92" s="4"/>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O92" s="4"/>
+      <c r="Z92"/>
+    </row>
+    <row r="93" spans="1:26">
       <c r="A93" s="3"/>
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
@@ -3192,8 +3366,10 @@
       <c r="L93" s="8"/>
       <c r="M93" s="4"/>
       <c r="N93" s="4"/>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O93" s="4"/>
+      <c r="Z93"/>
+    </row>
+    <row r="94" spans="1:26">
       <c r="A94" s="3"/>
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
@@ -3205,8 +3381,10 @@
       <c r="L94" s="8"/>
       <c r="M94" s="4"/>
       <c r="N94" s="4"/>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O94" s="4"/>
+      <c r="Z94"/>
+    </row>
+    <row r="95" spans="1:26">
       <c r="A95" s="3"/>
       <c r="D95" s="7"/>
       <c r="E95" s="7"/>
@@ -3218,8 +3396,10 @@
       <c r="L95" s="8"/>
       <c r="M95" s="4"/>
       <c r="N95" s="4"/>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O95" s="4"/>
+      <c r="Z95"/>
+    </row>
+    <row r="96" spans="1:26">
       <c r="A96" s="3"/>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
@@ -3231,8 +3411,10 @@
       <c r="L96" s="8"/>
       <c r="M96" s="4"/>
       <c r="N96" s="4"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O96" s="4"/>
+      <c r="Z96"/>
+    </row>
+    <row r="97" spans="1:26">
       <c r="A97" s="3"/>
       <c r="D97" s="7"/>
       <c r="E97" s="7"/>
@@ -3244,8 +3426,10 @@
       <c r="L97" s="8"/>
       <c r="M97" s="4"/>
       <c r="N97" s="4"/>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O97" s="4"/>
+      <c r="Z97"/>
+    </row>
+    <row r="98" spans="1:26">
       <c r="A98" s="3"/>
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
@@ -3257,8 +3441,10 @@
       <c r="L98" s="8"/>
       <c r="M98" s="4"/>
       <c r="N98" s="4"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O98" s="4"/>
+      <c r="Z98"/>
+    </row>
+    <row r="99" spans="1:26">
       <c r="A99" s="3"/>
       <c r="D99" s="7"/>
       <c r="E99" s="7"/>
@@ -3270,8 +3456,10 @@
       <c r="L99" s="8"/>
       <c r="M99" s="4"/>
       <c r="N99" s="4"/>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O99" s="4"/>
+      <c r="Z99"/>
+    </row>
+    <row r="100" spans="1:26">
       <c r="A100" s="3"/>
       <c r="D100" s="7"/>
       <c r="E100" s="7"/>
@@ -3283,8 +3471,10 @@
       <c r="L100" s="8"/>
       <c r="M100" s="4"/>
       <c r="N100" s="4"/>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O100" s="4"/>
+      <c r="Z100"/>
+    </row>
+    <row r="101" spans="1:26">
       <c r="A101" s="3"/>
       <c r="D101" s="7"/>
       <c r="E101" s="7"/>
@@ -3296,8 +3486,10 @@
       <c r="L101" s="8"/>
       <c r="M101" s="4"/>
       <c r="N101" s="4"/>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O101" s="4"/>
+      <c r="Z101"/>
+    </row>
+    <row r="102" spans="1:26">
       <c r="A102" s="3"/>
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
@@ -3309,8 +3501,10 @@
       <c r="L102" s="8"/>
       <c r="M102" s="4"/>
       <c r="N102" s="4"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O102" s="4"/>
+      <c r="Z102"/>
+    </row>
+    <row r="103" spans="1:26">
       <c r="A103" s="3"/>
       <c r="D103" s="7"/>
       <c r="E103" s="7"/>
@@ -3322,8 +3516,10 @@
       <c r="L103" s="8"/>
       <c r="M103" s="4"/>
       <c r="N103" s="4"/>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O103" s="4"/>
+      <c r="Z103"/>
+    </row>
+    <row r="104" spans="1:26">
       <c r="A104" s="3"/>
       <c r="D104" s="7"/>
       <c r="E104" s="7"/>
@@ -3335,8 +3531,10 @@
       <c r="L104" s="8"/>
       <c r="M104" s="4"/>
       <c r="N104" s="4"/>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O104" s="4"/>
+      <c r="Z104"/>
+    </row>
+    <row r="105" spans="1:26">
       <c r="A105" s="3"/>
       <c r="D105" s="7"/>
       <c r="E105" s="7"/>
@@ -3348,8 +3546,10 @@
       <c r="L105" s="8"/>
       <c r="M105" s="4"/>
       <c r="N105" s="4"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O105" s="4"/>
+      <c r="Z105"/>
+    </row>
+    <row r="106" spans="1:26">
       <c r="A106" s="3"/>
       <c r="D106" s="7"/>
       <c r="E106" s="7"/>
@@ -3361,8 +3561,10 @@
       <c r="L106" s="8"/>
       <c r="M106" s="4"/>
       <c r="N106" s="4"/>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O106" s="4"/>
+      <c r="Z106"/>
+    </row>
+    <row r="107" spans="1:26">
       <c r="A107" s="3"/>
       <c r="D107" s="7"/>
       <c r="E107" s="7"/>
@@ -3374,8 +3576,10 @@
       <c r="L107" s="8"/>
       <c r="M107" s="4"/>
       <c r="N107" s="4"/>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O107" s="4"/>
+      <c r="Z107"/>
+    </row>
+    <row r="108" spans="1:26">
       <c r="A108" s="3"/>
       <c r="D108" s="7"/>
       <c r="E108" s="7"/>
@@ -3387,8 +3591,10 @@
       <c r="L108" s="8"/>
       <c r="M108" s="4"/>
       <c r="N108" s="4"/>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O108" s="4"/>
+      <c r="Z108"/>
+    </row>
+    <row r="109" spans="1:26">
       <c r="A109" s="3"/>
       <c r="D109" s="7"/>
       <c r="E109" s="7"/>
@@ -3400,8 +3606,10 @@
       <c r="L109" s="8"/>
       <c r="M109" s="4"/>
       <c r="N109" s="4"/>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O109" s="4"/>
+      <c r="Z109"/>
+    </row>
+    <row r="110" spans="1:26">
       <c r="A110" s="3"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7"/>
@@ -3413,8 +3621,10 @@
       <c r="L110" s="8"/>
       <c r="M110" s="4"/>
       <c r="N110" s="4"/>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O110" s="4"/>
+      <c r="Z110"/>
+    </row>
+    <row r="111" spans="1:26">
       <c r="A111" s="3"/>
       <c r="D111" s="7"/>
       <c r="E111" s="7"/>
@@ -3426,8 +3636,10 @@
       <c r="L111" s="8"/>
       <c r="M111" s="4"/>
       <c r="N111" s="4"/>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O111" s="4"/>
+      <c r="Z111"/>
+    </row>
+    <row r="112" spans="1:26">
       <c r="A112" s="3"/>
       <c r="D112" s="7"/>
       <c r="E112" s="7"/>
@@ -3439,8 +3651,10 @@
       <c r="L112" s="8"/>
       <c r="M112" s="4"/>
       <c r="N112" s="4"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O112" s="4"/>
+      <c r="Z112"/>
+    </row>
+    <row r="113" spans="1:26">
       <c r="A113" s="3"/>
       <c r="D113" s="7"/>
       <c r="E113" s="7"/>
@@ -3452,8 +3666,10 @@
       <c r="L113" s="8"/>
       <c r="M113" s="4"/>
       <c r="N113" s="4"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O113" s="4"/>
+      <c r="Z113"/>
+    </row>
+    <row r="114" spans="1:26">
       <c r="A114" s="3"/>
       <c r="D114" s="7"/>
       <c r="E114" s="7"/>
@@ -3465,8 +3681,10 @@
       <c r="L114" s="8"/>
       <c r="M114" s="4"/>
       <c r="N114" s="4"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O114" s="4"/>
+      <c r="Z114"/>
+    </row>
+    <row r="115" spans="1:26">
       <c r="A115" s="3"/>
       <c r="D115" s="7"/>
       <c r="E115" s="7"/>
@@ -3478,8 +3696,10 @@
       <c r="L115" s="8"/>
       <c r="M115" s="4"/>
       <c r="N115" s="4"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O115" s="4"/>
+      <c r="Z115"/>
+    </row>
+    <row r="116" spans="1:26">
       <c r="A116" s="3"/>
       <c r="D116" s="7"/>
       <c r="E116" s="7"/>
@@ -3491,8 +3711,10 @@
       <c r="L116" s="8"/>
       <c r="M116" s="4"/>
       <c r="N116" s="4"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O116" s="4"/>
+      <c r="Z116"/>
+    </row>
+    <row r="117" spans="1:26">
       <c r="A117" s="3"/>
       <c r="D117" s="7"/>
       <c r="E117" s="7"/>
@@ -3504,8 +3726,10 @@
       <c r="L117" s="8"/>
       <c r="M117" s="4"/>
       <c r="N117" s="4"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O117" s="4"/>
+      <c r="Z117"/>
+    </row>
+    <row r="118" spans="1:26">
       <c r="A118" s="3"/>
       <c r="D118" s="7"/>
       <c r="E118" s="7"/>
@@ -3517,8 +3741,10 @@
       <c r="L118" s="8"/>
       <c r="M118" s="4"/>
       <c r="N118" s="4"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O118" s="4"/>
+      <c r="Z118"/>
+    </row>
+    <row r="119" spans="1:26">
       <c r="A119" s="3"/>
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
@@ -3530,8 +3756,10 @@
       <c r="L119" s="8"/>
       <c r="M119" s="4"/>
       <c r="N119" s="4"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O119" s="4"/>
+      <c r="Z119"/>
+    </row>
+    <row r="120" spans="1:26">
       <c r="A120" s="3"/>
       <c r="D120" s="7"/>
       <c r="E120" s="7"/>
@@ -3543,8 +3771,10 @@
       <c r="L120" s="8"/>
       <c r="M120" s="4"/>
       <c r="N120" s="4"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O120" s="4"/>
+      <c r="Z120"/>
+    </row>
+    <row r="121" spans="1:26">
       <c r="A121" s="3"/>
       <c r="D121" s="7"/>
       <c r="E121" s="7"/>
@@ -3556,8 +3786,10 @@
       <c r="L121" s="8"/>
       <c r="M121" s="4"/>
       <c r="N121" s="4"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O121" s="4"/>
+      <c r="Z121"/>
+    </row>
+    <row r="122" spans="1:26">
       <c r="A122" s="3"/>
       <c r="D122" s="7"/>
       <c r="E122" s="7"/>
@@ -3569,8 +3801,10 @@
       <c r="L122" s="8"/>
       <c r="M122" s="4"/>
       <c r="N122" s="4"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O122" s="4"/>
+      <c r="Z122"/>
+    </row>
+    <row r="123" spans="1:26">
       <c r="A123" s="3"/>
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
@@ -3582,8 +3816,10 @@
       <c r="L123" s="8"/>
       <c r="M123" s="4"/>
       <c r="N123" s="4"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O123" s="4"/>
+      <c r="Z123"/>
+    </row>
+    <row r="124" spans="1:26">
       <c r="A124" s="3"/>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
@@ -3595,8 +3831,10 @@
       <c r="L124" s="8"/>
       <c r="M124" s="4"/>
       <c r="N124" s="4"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O124" s="4"/>
+      <c r="Z124"/>
+    </row>
+    <row r="125" spans="1:26">
       <c r="A125" s="3"/>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
@@ -3608,8 +3846,10 @@
       <c r="L125" s="8"/>
       <c r="M125" s="4"/>
       <c r="N125" s="4"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O125" s="4"/>
+      <c r="Z125"/>
+    </row>
+    <row r="126" spans="1:26">
       <c r="A126" s="3"/>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
@@ -3621,8 +3861,10 @@
       <c r="L126" s="8"/>
       <c r="M126" s="4"/>
       <c r="N126" s="4"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O126" s="4"/>
+      <c r="Z126"/>
+    </row>
+    <row r="127" spans="1:26">
       <c r="A127" s="3"/>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
@@ -3634,8 +3876,10 @@
       <c r="L127" s="8"/>
       <c r="M127" s="4"/>
       <c r="N127" s="4"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O127" s="4"/>
+      <c r="Z127"/>
+    </row>
+    <row r="128" spans="1:26">
       <c r="A128" s="3"/>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
@@ -3647,8 +3891,10 @@
       <c r="L128" s="8"/>
       <c r="M128" s="4"/>
       <c r="N128" s="4"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O128" s="4"/>
+      <c r="Z128"/>
+    </row>
+    <row r="129" spans="1:26">
       <c r="A129" s="3"/>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
@@ -3660,8 +3906,10 @@
       <c r="L129" s="8"/>
       <c r="M129" s="4"/>
       <c r="N129" s="4"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O129" s="4"/>
+      <c r="Z129"/>
+    </row>
+    <row r="130" spans="1:26">
       <c r="A130" s="3"/>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
@@ -3673,8 +3921,10 @@
       <c r="L130" s="8"/>
       <c r="M130" s="4"/>
       <c r="N130" s="4"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O130" s="4"/>
+      <c r="Z130"/>
+    </row>
+    <row r="131" spans="1:26">
       <c r="A131" s="3"/>
       <c r="D131" s="7"/>
       <c r="E131" s="7"/>
@@ -3686,8 +3936,10 @@
       <c r="L131" s="8"/>
       <c r="M131" s="4"/>
       <c r="N131" s="4"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O131" s="4"/>
+      <c r="Z131"/>
+    </row>
+    <row r="132" spans="1:26">
       <c r="A132" s="3"/>
       <c r="D132" s="7"/>
       <c r="E132" s="7"/>
@@ -3699,8 +3951,10 @@
       <c r="L132" s="8"/>
       <c r="M132" s="4"/>
       <c r="N132" s="4"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O132" s="4"/>
+      <c r="Z132"/>
+    </row>
+    <row r="133" spans="1:26">
       <c r="A133" s="3"/>
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
@@ -3712,8 +3966,10 @@
       <c r="L133" s="8"/>
       <c r="M133" s="4"/>
       <c r="N133" s="4"/>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O133" s="4"/>
+      <c r="Z133"/>
+    </row>
+    <row r="134" spans="1:26">
       <c r="A134" s="3"/>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
@@ -3725,8 +3981,10 @@
       <c r="L134" s="8"/>
       <c r="M134" s="4"/>
       <c r="N134" s="4"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O134" s="4"/>
+      <c r="Z134"/>
+    </row>
+    <row r="135" spans="1:26">
       <c r="A135" s="3"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
@@ -3738,8 +3996,10 @@
       <c r="L135" s="8"/>
       <c r="M135" s="4"/>
       <c r="N135" s="4"/>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O135" s="4"/>
+      <c r="Z135"/>
+    </row>
+    <row r="136" spans="1:26">
       <c r="A136" s="3"/>
       <c r="D136" s="7"/>
       <c r="E136" s="7"/>
@@ -3751,8 +4011,10 @@
       <c r="L136" s="8"/>
       <c r="M136" s="4"/>
       <c r="N136" s="4"/>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O136" s="4"/>
+      <c r="Z136"/>
+    </row>
+    <row r="137" spans="1:26">
       <c r="A137" s="3"/>
       <c r="D137" s="7"/>
       <c r="E137" s="7"/>
@@ -3764,8 +4026,10 @@
       <c r="L137" s="8"/>
       <c r="M137" s="4"/>
       <c r="N137" s="4"/>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O137" s="4"/>
+      <c r="Z137"/>
+    </row>
+    <row r="138" spans="1:26">
       <c r="A138" s="3"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
@@ -3777,8 +4041,10 @@
       <c r="L138" s="8"/>
       <c r="M138" s="4"/>
       <c r="N138" s="4"/>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O138" s="4"/>
+      <c r="Z138"/>
+    </row>
+    <row r="139" spans="1:26">
       <c r="A139" s="3"/>
       <c r="D139" s="7"/>
       <c r="E139" s="7"/>
@@ -3790,8 +4056,10 @@
       <c r="L139" s="8"/>
       <c r="M139" s="4"/>
       <c r="N139" s="4"/>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O139" s="4"/>
+      <c r="Z139"/>
+    </row>
+    <row r="140" spans="1:26">
       <c r="A140" s="3"/>
       <c r="D140" s="7"/>
       <c r="E140" s="7"/>
@@ -3803,8 +4071,10 @@
       <c r="L140" s="8"/>
       <c r="M140" s="4"/>
       <c r="N140" s="4"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O140" s="4"/>
+      <c r="Z140"/>
+    </row>
+    <row r="141" spans="1:26">
       <c r="A141" s="3"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7"/>
@@ -3816,8 +4086,10 @@
       <c r="L141" s="8"/>
       <c r="M141" s="4"/>
       <c r="N141" s="4"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O141" s="4"/>
+      <c r="Z141"/>
+    </row>
+    <row r="142" spans="1:26">
       <c r="A142" s="3"/>
       <c r="D142" s="7"/>
       <c r="E142" s="7"/>
@@ -3829,8 +4101,10 @@
       <c r="L142" s="8"/>
       <c r="M142" s="4"/>
       <c r="N142" s="4"/>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O142" s="4"/>
+      <c r="Z142"/>
+    </row>
+    <row r="143" spans="1:26">
       <c r="A143" s="3"/>
       <c r="D143" s="7"/>
       <c r="E143" s="7"/>
@@ -3842,8 +4116,10 @@
       <c r="L143" s="8"/>
       <c r="M143" s="4"/>
       <c r="N143" s="4"/>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O143" s="4"/>
+      <c r="Z143"/>
+    </row>
+    <row r="144" spans="1:26">
       <c r="A144" s="3"/>
       <c r="D144" s="7"/>
       <c r="E144" s="7"/>
@@ -3855,8 +4131,10 @@
       <c r="L144" s="8"/>
       <c r="M144" s="4"/>
       <c r="N144" s="4"/>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O144" s="4"/>
+      <c r="Z144"/>
+    </row>
+    <row r="145" spans="1:26">
       <c r="A145" s="3"/>
       <c r="D145" s="7"/>
       <c r="E145" s="7"/>
@@ -3868,8 +4146,10 @@
       <c r="L145" s="8"/>
       <c r="M145" s="4"/>
       <c r="N145" s="4"/>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O145" s="4"/>
+      <c r="Z145"/>
+    </row>
+    <row r="146" spans="1:26">
       <c r="A146" s="3"/>
       <c r="D146" s="7"/>
       <c r="E146" s="7"/>
@@ -3881,8 +4161,10 @@
       <c r="L146" s="8"/>
       <c r="M146" s="4"/>
       <c r="N146" s="4"/>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O146" s="4"/>
+      <c r="Z146"/>
+    </row>
+    <row r="147" spans="1:26">
       <c r="A147" s="3"/>
       <c r="D147" s="7"/>
       <c r="E147" s="7"/>
@@ -3894,8 +4176,10 @@
       <c r="L147" s="8"/>
       <c r="M147" s="4"/>
       <c r="N147" s="4"/>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O147" s="4"/>
+      <c r="Z147"/>
+    </row>
+    <row r="148" spans="1:26">
       <c r="A148" s="3"/>
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
@@ -3907,8 +4191,10 @@
       <c r="L148" s="8"/>
       <c r="M148" s="4"/>
       <c r="N148" s="4"/>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O148" s="4"/>
+      <c r="Z148"/>
+    </row>
+    <row r="149" spans="1:26">
       <c r="A149" s="3"/>
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
@@ -3920,8 +4206,10 @@
       <c r="L149" s="8"/>
       <c r="M149" s="4"/>
       <c r="N149" s="4"/>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O149" s="4"/>
+      <c r="Z149"/>
+    </row>
+    <row r="150" spans="1:26">
       <c r="A150" s="3"/>
       <c r="D150" s="7"/>
       <c r="E150" s="7"/>
@@ -3933,8 +4221,10 @@
       <c r="L150" s="8"/>
       <c r="M150" s="4"/>
       <c r="N150" s="4"/>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O150" s="4"/>
+      <c r="Z150"/>
+    </row>
+    <row r="151" spans="1:26">
       <c r="A151" s="3"/>
       <c r="D151" s="7"/>
       <c r="E151" s="7"/>
@@ -3946,8 +4236,10 @@
       <c r="L151" s="8"/>
       <c r="M151" s="4"/>
       <c r="N151" s="4"/>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O151" s="4"/>
+      <c r="Z151"/>
+    </row>
+    <row r="152" spans="1:26">
       <c r="A152" s="3"/>
       <c r="D152" s="7"/>
       <c r="E152" s="7"/>
@@ -3959,8 +4251,10 @@
       <c r="L152" s="8"/>
       <c r="M152" s="4"/>
       <c r="N152" s="4"/>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O152" s="4"/>
+      <c r="Z152"/>
+    </row>
+    <row r="153" spans="1:26">
       <c r="A153" s="3"/>
       <c r="D153" s="7"/>
       <c r="E153" s="7"/>
@@ -3972,8 +4266,10 @@
       <c r="L153" s="8"/>
       <c r="M153" s="4"/>
       <c r="N153" s="4"/>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O153" s="4"/>
+      <c r="Z153"/>
+    </row>
+    <row r="154" spans="1:26">
       <c r="A154" s="3"/>
       <c r="D154" s="7"/>
       <c r="E154" s="7"/>
@@ -3985,8 +4281,10 @@
       <c r="L154" s="8"/>
       <c r="M154" s="4"/>
       <c r="N154" s="4"/>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O154" s="4"/>
+      <c r="Z154"/>
+    </row>
+    <row r="155" spans="1:26">
       <c r="A155" s="3"/>
       <c r="D155" s="7"/>
       <c r="E155" s="7"/>
@@ -3998,8 +4296,10 @@
       <c r="L155" s="8"/>
       <c r="M155" s="4"/>
       <c r="N155" s="4"/>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O155" s="4"/>
+      <c r="Z155"/>
+    </row>
+    <row r="156" spans="1:26">
       <c r="A156" s="3"/>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
@@ -4011,8 +4311,10 @@
       <c r="L156" s="8"/>
       <c r="M156" s="4"/>
       <c r="N156" s="4"/>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O156" s="4"/>
+      <c r="Z156"/>
+    </row>
+    <row r="157" spans="1:26">
       <c r="A157" s="3"/>
       <c r="D157" s="7"/>
       <c r="E157" s="7"/>
@@ -4024,8 +4326,10 @@
       <c r="L157" s="8"/>
       <c r="M157" s="4"/>
       <c r="N157" s="4"/>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O157" s="4"/>
+      <c r="Z157"/>
+    </row>
+    <row r="158" spans="1:26">
       <c r="A158" s="3"/>
       <c r="D158" s="7"/>
       <c r="E158" s="7"/>
@@ -4037,8 +4341,10 @@
       <c r="L158" s="8"/>
       <c r="M158" s="4"/>
       <c r="N158" s="4"/>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O158" s="4"/>
+      <c r="Z158"/>
+    </row>
+    <row r="159" spans="1:26">
       <c r="A159" s="3"/>
       <c r="D159" s="7"/>
       <c r="E159" s="7"/>
@@ -4050,8 +4356,10 @@
       <c r="L159" s="8"/>
       <c r="M159" s="4"/>
       <c r="N159" s="4"/>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O159" s="4"/>
+      <c r="Z159"/>
+    </row>
+    <row r="160" spans="1:26">
       <c r="A160" s="3"/>
       <c r="D160" s="7"/>
       <c r="E160" s="7"/>
@@ -4063,8 +4371,10 @@
       <c r="L160" s="8"/>
       <c r="M160" s="4"/>
       <c r="N160" s="4"/>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O160" s="4"/>
+      <c r="Z160"/>
+    </row>
+    <row r="161" spans="1:26">
       <c r="A161" s="3"/>
       <c r="D161" s="7"/>
       <c r="E161" s="7"/>
@@ -4076,8 +4386,10 @@
       <c r="L161" s="8"/>
       <c r="M161" s="4"/>
       <c r="N161" s="4"/>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O161" s="4"/>
+      <c r="Z161"/>
+    </row>
+    <row r="162" spans="1:26">
       <c r="A162" s="3"/>
       <c r="D162" s="7"/>
       <c r="E162" s="7"/>
@@ -4089,8 +4401,10 @@
       <c r="L162" s="8"/>
       <c r="M162" s="4"/>
       <c r="N162" s="4"/>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O162" s="4"/>
+      <c r="Z162"/>
+    </row>
+    <row r="163" spans="1:26">
       <c r="A163" s="3"/>
       <c r="D163" s="7"/>
       <c r="E163" s="7"/>
@@ -4102,8 +4416,10 @@
       <c r="L163" s="8"/>
       <c r="M163" s="4"/>
       <c r="N163" s="4"/>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O163" s="4"/>
+      <c r="Z163"/>
+    </row>
+    <row r="164" spans="1:26">
       <c r="A164" s="3"/>
       <c r="D164" s="7"/>
       <c r="E164" s="7"/>
@@ -4115,8 +4431,10 @@
       <c r="L164" s="8"/>
       <c r="M164" s="4"/>
       <c r="N164" s="4"/>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O164" s="4"/>
+      <c r="Z164"/>
+    </row>
+    <row r="165" spans="1:26">
       <c r="A165" s="3"/>
       <c r="D165" s="7"/>
       <c r="E165" s="7"/>
@@ -4128,8 +4446,10 @@
       <c r="L165" s="8"/>
       <c r="M165" s="4"/>
       <c r="N165" s="4"/>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O165" s="4"/>
+      <c r="Z165"/>
+    </row>
+    <row r="166" spans="1:26">
       <c r="A166" s="3"/>
       <c r="D166" s="7"/>
       <c r="E166" s="7"/>
@@ -4141,8 +4461,10 @@
       <c r="L166" s="8"/>
       <c r="M166" s="4"/>
       <c r="N166" s="4"/>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O166" s="4"/>
+      <c r="Z166"/>
+    </row>
+    <row r="167" spans="1:26">
       <c r="A167" s="3"/>
       <c r="D167" s="7"/>
       <c r="E167" s="7"/>
@@ -4154,8 +4476,10 @@
       <c r="L167" s="8"/>
       <c r="M167" s="4"/>
       <c r="N167" s="4"/>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O167" s="4"/>
+      <c r="Z167"/>
+    </row>
+    <row r="168" spans="1:26">
       <c r="A168" s="3"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
@@ -4167,8 +4491,10 @@
       <c r="L168" s="8"/>
       <c r="M168" s="4"/>
       <c r="N168" s="4"/>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O168" s="4"/>
+      <c r="Z168"/>
+    </row>
+    <row r="169" spans="1:26">
       <c r="A169" s="3"/>
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
@@ -4180,8 +4506,10 @@
       <c r="L169" s="8"/>
       <c r="M169" s="4"/>
       <c r="N169" s="4"/>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O169" s="4"/>
+      <c r="Z169"/>
+    </row>
+    <row r="170" spans="1:26">
       <c r="A170" s="3"/>
       <c r="D170" s="7"/>
       <c r="E170" s="7"/>
@@ -4193,8 +4521,10 @@
       <c r="L170" s="8"/>
       <c r="M170" s="4"/>
       <c r="N170" s="4"/>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O170" s="4"/>
+      <c r="Z170"/>
+    </row>
+    <row r="171" spans="1:26">
       <c r="A171" s="3"/>
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
@@ -4206,8 +4536,10 @@
       <c r="L171" s="8"/>
       <c r="M171" s="4"/>
       <c r="N171" s="4"/>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O171" s="4"/>
+      <c r="Z171"/>
+    </row>
+    <row r="172" spans="1:26">
       <c r="A172" s="3"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
@@ -4219,8 +4551,10 @@
       <c r="L172" s="8"/>
       <c r="M172" s="4"/>
       <c r="N172" s="4"/>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O172" s="4"/>
+      <c r="Z172"/>
+    </row>
+    <row r="173" spans="1:26">
       <c r="A173" s="3"/>
       <c r="D173" s="7"/>
       <c r="E173" s="7"/>
@@ -4232,8 +4566,10 @@
       <c r="L173" s="8"/>
       <c r="M173" s="4"/>
       <c r="N173" s="4"/>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O173" s="4"/>
+      <c r="Z173"/>
+    </row>
+    <row r="174" spans="1:26">
       <c r="A174" s="3"/>
       <c r="D174" s="7"/>
       <c r="E174" s="7"/>
@@ -4245,8 +4581,10 @@
       <c r="L174" s="8"/>
       <c r="M174" s="4"/>
       <c r="N174" s="4"/>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O174" s="4"/>
+      <c r="Z174"/>
+    </row>
+    <row r="175" spans="1:26">
       <c r="A175" s="3"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
@@ -4258,8 +4596,10 @@
       <c r="L175" s="8"/>
       <c r="M175" s="4"/>
       <c r="N175" s="4"/>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O175" s="4"/>
+      <c r="Z175"/>
+    </row>
+    <row r="176" spans="1:26">
       <c r="A176" s="3"/>
       <c r="D176" s="7"/>
       <c r="E176" s="7"/>
@@ -4271,8 +4611,10 @@
       <c r="L176" s="8"/>
       <c r="M176" s="4"/>
       <c r="N176" s="4"/>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O176" s="4"/>
+      <c r="Z176"/>
+    </row>
+    <row r="177" spans="1:26">
       <c r="A177" s="3"/>
       <c r="D177" s="7"/>
       <c r="E177" s="7"/>
@@ -4284,8 +4626,10 @@
       <c r="L177" s="8"/>
       <c r="M177" s="4"/>
       <c r="N177" s="4"/>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O177" s="4"/>
+      <c r="Z177"/>
+    </row>
+    <row r="178" spans="1:26">
       <c r="A178" s="3"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7"/>
@@ -4297,8 +4641,10 @@
       <c r="L178" s="8"/>
       <c r="M178" s="4"/>
       <c r="N178" s="4"/>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O178" s="4"/>
+      <c r="Z178"/>
+    </row>
+    <row r="179" spans="1:26">
       <c r="A179" s="3"/>
       <c r="D179" s="7"/>
       <c r="E179" s="7"/>
@@ -4310,8 +4656,10 @@
       <c r="L179" s="8"/>
       <c r="M179" s="4"/>
       <c r="N179" s="4"/>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O179" s="4"/>
+      <c r="Z179"/>
+    </row>
+    <row r="180" spans="1:26">
       <c r="A180" s="3"/>
       <c r="D180" s="7"/>
       <c r="E180" s="7"/>
@@ -4323,8 +4671,10 @@
       <c r="L180" s="8"/>
       <c r="M180" s="4"/>
       <c r="N180" s="4"/>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O180" s="4"/>
+      <c r="Z180"/>
+    </row>
+    <row r="181" spans="1:26">
       <c r="A181" s="3"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7"/>
@@ -4336,8 +4686,10 @@
       <c r="L181" s="8"/>
       <c r="M181" s="4"/>
       <c r="N181" s="4"/>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O181" s="4"/>
+      <c r="Z181"/>
+    </row>
+    <row r="182" spans="1:26">
       <c r="A182" s="3"/>
       <c r="D182" s="7"/>
       <c r="E182" s="7"/>
@@ -4349,8 +4701,10 @@
       <c r="L182" s="8"/>
       <c r="M182" s="4"/>
       <c r="N182" s="4"/>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O182" s="4"/>
+      <c r="Z182"/>
+    </row>
+    <row r="183" spans="1:26">
       <c r="A183" s="3"/>
       <c r="D183" s="7"/>
       <c r="E183" s="7"/>
@@ -4362,8 +4716,10 @@
       <c r="L183" s="8"/>
       <c r="M183" s="4"/>
       <c r="N183" s="4"/>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O183" s="4"/>
+      <c r="Z183"/>
+    </row>
+    <row r="184" spans="1:26">
       <c r="A184" s="3"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
@@ -4375,8 +4731,10 @@
       <c r="L184" s="8"/>
       <c r="M184" s="4"/>
       <c r="N184" s="4"/>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O184" s="4"/>
+      <c r="Z184"/>
+    </row>
+    <row r="185" spans="1:26">
       <c r="A185" s="3"/>
       <c r="D185" s="7"/>
       <c r="E185" s="7"/>
@@ -4388,8 +4746,10 @@
       <c r="L185" s="8"/>
       <c r="M185" s="4"/>
       <c r="N185" s="4"/>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O185" s="4"/>
+      <c r="Z185"/>
+    </row>
+    <row r="186" spans="1:26">
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
       <c r="F186" s="7"/>
@@ -4398,8 +4758,9 @@
       <c r="I186" s="7"/>
       <c r="K186" s="1"/>
       <c r="L186" s="8"/>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Z186"/>
+    </row>
+    <row r="187" spans="1:26">
       <c r="D187" s="7"/>
       <c r="E187" s="7"/>
       <c r="F187" s="7"/>
@@ -4408,8 +4769,9 @@
       <c r="I187" s="7"/>
       <c r="K187" s="1"/>
       <c r="L187" s="8"/>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Z187"/>
+    </row>
+    <row r="188" spans="1:26">
       <c r="D188" s="7"/>
       <c r="E188" s="7"/>
       <c r="F188" s="7"/>
@@ -4418,8 +4780,9 @@
       <c r="I188" s="7"/>
       <c r="K188" s="1"/>
       <c r="L188" s="8"/>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Z188"/>
+    </row>
+    <row r="189" spans="1:26">
       <c r="D189" s="7"/>
       <c r="E189" s="7"/>
       <c r="F189" s="7"/>
@@ -4428,8 +4791,9 @@
       <c r="I189" s="7"/>
       <c r="K189" s="1"/>
       <c r="L189" s="8"/>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Z189"/>
+    </row>
+    <row r="190" spans="1:26">
       <c r="D190" s="7"/>
       <c r="E190" s="7"/>
       <c r="F190" s="7"/>
@@ -4438,8 +4802,9 @@
       <c r="I190" s="7"/>
       <c r="K190" s="1"/>
       <c r="L190" s="8"/>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Z190"/>
+    </row>
+    <row r="191" spans="1:26">
       <c r="D191" s="7"/>
       <c r="E191" s="7"/>
       <c r="F191" s="7"/>
@@ -4448,8 +4813,9 @@
       <c r="I191" s="7"/>
       <c r="K191" s="1"/>
       <c r="L191" s="8"/>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Z191"/>
+    </row>
+    <row r="192" spans="1:26">
       <c r="D192" s="7"/>
       <c r="E192" s="7"/>
       <c r="F192" s="7"/>
@@ -4458,408 +4824,551 @@
       <c r="I192" s="7"/>
       <c r="K192" s="1"/>
       <c r="L192" s="8"/>
-    </row>
-    <row r="193" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z192"/>
+    </row>
+    <row r="193" spans="1:26">
       <c r="K193" s="1"/>
-    </row>
-    <row r="194" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z193"/>
+    </row>
+    <row r="194" spans="1:26">
       <c r="K194" s="1"/>
-    </row>
-    <row r="195" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z194"/>
+    </row>
+    <row r="195" spans="1:26">
       <c r="K195" s="1"/>
-    </row>
-    <row r="196" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z195"/>
+    </row>
+    <row r="196" spans="1:26">
       <c r="K196" s="1"/>
-    </row>
-    <row r="197" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z196"/>
+    </row>
+    <row r="197" spans="1:26">
       <c r="K197" s="1"/>
-    </row>
-    <row r="198" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z197"/>
+    </row>
+    <row r="198" spans="1:26">
       <c r="K198" s="1"/>
-    </row>
-    <row r="199" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z198"/>
+    </row>
+    <row r="199" spans="1:26">
       <c r="K199" s="1"/>
-    </row>
-    <row r="200" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z199"/>
+    </row>
+    <row r="200" spans="1:26">
       <c r="K200" s="1"/>
-    </row>
-    <row r="201" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z200"/>
+    </row>
+    <row r="201" spans="1:26">
       <c r="K201" s="1"/>
-    </row>
-    <row r="202" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z201"/>
+    </row>
+    <row r="202" spans="1:26">
       <c r="K202" s="1"/>
-    </row>
-    <row r="203" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z202"/>
+    </row>
+    <row r="203" spans="1:26">
       <c r="K203" s="1"/>
-    </row>
-    <row r="204" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z203"/>
+    </row>
+    <row r="204" spans="1:26">
       <c r="K204" s="1"/>
-    </row>
-    <row r="205" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z204"/>
+    </row>
+    <row r="205" spans="1:26">
       <c r="K205" s="1"/>
-    </row>
-    <row r="206" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z205"/>
+    </row>
+    <row r="206" spans="1:26">
       <c r="K206" s="1"/>
-    </row>
-    <row r="207" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z206"/>
+    </row>
+    <row r="207" spans="1:26">
       <c r="K207" s="1"/>
-    </row>
-    <row r="208" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z207"/>
+    </row>
+    <row r="208" spans="1:26">
       <c r="K208" s="1"/>
-    </row>
-    <row r="209" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z208"/>
+    </row>
+    <row r="209" spans="1:26">
       <c r="K209" s="1"/>
-    </row>
-    <row r="210" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z209"/>
+    </row>
+    <row r="210" spans="1:26">
       <c r="K210" s="1"/>
-    </row>
-    <row r="211" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z210"/>
+    </row>
+    <row r="211" spans="1:26">
       <c r="K211" s="1"/>
-    </row>
-    <row r="212" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z211"/>
+    </row>
+    <row r="212" spans="1:26">
       <c r="K212" s="1"/>
-    </row>
-    <row r="213" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z212"/>
+    </row>
+    <row r="213" spans="1:26">
       <c r="K213" s="1"/>
-    </row>
-    <row r="214" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z213"/>
+    </row>
+    <row r="214" spans="1:26">
       <c r="K214" s="1"/>
-    </row>
-    <row r="215" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z214"/>
+    </row>
+    <row r="215" spans="1:26">
       <c r="K215" s="1"/>
-    </row>
-    <row r="216" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z215"/>
+    </row>
+    <row r="216" spans="1:26">
       <c r="K216" s="1"/>
-    </row>
-    <row r="217" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z216"/>
+    </row>
+    <row r="217" spans="1:26">
       <c r="K217" s="1"/>
-    </row>
-    <row r="218" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z217"/>
+    </row>
+    <row r="218" spans="1:26">
       <c r="K218" s="1"/>
-    </row>
-    <row r="219" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z218"/>
+    </row>
+    <row r="219" spans="1:26">
       <c r="K219" s="1"/>
-    </row>
-    <row r="220" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z219"/>
+    </row>
+    <row r="220" spans="1:26">
       <c r="K220" s="1"/>
-    </row>
-    <row r="221" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z220"/>
+    </row>
+    <row r="221" spans="1:26">
       <c r="K221" s="1"/>
-    </row>
-    <row r="222" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z221"/>
+    </row>
+    <row r="222" spans="1:26">
       <c r="K222" s="1"/>
-    </row>
-    <row r="223" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z222"/>
+    </row>
+    <row r="223" spans="1:26">
       <c r="K223" s="1"/>
-    </row>
-    <row r="224" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z223"/>
+    </row>
+    <row r="224" spans="1:26">
       <c r="K224" s="1"/>
-    </row>
-    <row r="225" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z224"/>
+    </row>
+    <row r="225" spans="1:26">
       <c r="K225" s="1"/>
-    </row>
-    <row r="226" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z225"/>
+    </row>
+    <row r="226" spans="1:26">
       <c r="K226" s="1"/>
-    </row>
-    <row r="227" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z226"/>
+    </row>
+    <row r="227" spans="1:26">
       <c r="K227" s="1"/>
-    </row>
-    <row r="228" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z227"/>
+    </row>
+    <row r="228" spans="1:26">
       <c r="K228" s="1"/>
-    </row>
-    <row r="229" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z228"/>
+    </row>
+    <row r="229" spans="1:26">
       <c r="K229" s="1"/>
-    </row>
-    <row r="230" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z229"/>
+    </row>
+    <row r="230" spans="1:26">
       <c r="K230" s="1"/>
-    </row>
-    <row r="231" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z230"/>
+    </row>
+    <row r="231" spans="1:26">
       <c r="K231" s="1"/>
-    </row>
-    <row r="232" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z231"/>
+    </row>
+    <row r="232" spans="1:26">
       <c r="K232" s="1"/>
-    </row>
-    <row r="233" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z232"/>
+    </row>
+    <row r="233" spans="1:26">
       <c r="K233" s="1"/>
-    </row>
-    <row r="234" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z233"/>
+    </row>
+    <row r="234" spans="1:26">
       <c r="K234" s="1"/>
-    </row>
-    <row r="235" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z234"/>
+    </row>
+    <row r="235" spans="1:26">
       <c r="K235" s="1"/>
-    </row>
-    <row r="236" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z235"/>
+    </row>
+    <row r="236" spans="1:26">
       <c r="K236" s="1"/>
-    </row>
-    <row r="237" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z236"/>
+    </row>
+    <row r="237" spans="1:26">
       <c r="K237" s="1"/>
-    </row>
-    <row r="238" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z237"/>
+    </row>
+    <row r="238" spans="1:26">
       <c r="K238" s="1"/>
-    </row>
-    <row r="239" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z238"/>
+    </row>
+    <row r="239" spans="1:26">
       <c r="K239" s="1"/>
-    </row>
-    <row r="240" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z239"/>
+    </row>
+    <row r="240" spans="1:26">
       <c r="K240" s="1"/>
-    </row>
-    <row r="241" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z240"/>
+    </row>
+    <row r="241" spans="1:26">
       <c r="K241" s="1"/>
-    </row>
-    <row r="242" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z241"/>
+    </row>
+    <row r="242" spans="1:26">
       <c r="K242" s="1"/>
-    </row>
-    <row r="243" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z242"/>
+    </row>
+    <row r="243" spans="1:26">
       <c r="K243" s="1"/>
-    </row>
-    <row r="244" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z243"/>
+    </row>
+    <row r="244" spans="1:26">
       <c r="K244" s="1"/>
-    </row>
-    <row r="245" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z244"/>
+    </row>
+    <row r="245" spans="1:26">
       <c r="K245" s="1"/>
-    </row>
-    <row r="246" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z245"/>
+    </row>
+    <row r="246" spans="1:26">
       <c r="K246" s="1"/>
-    </row>
-    <row r="247" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z246"/>
+    </row>
+    <row r="247" spans="1:26">
       <c r="K247" s="1"/>
-    </row>
-    <row r="248" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z247"/>
+    </row>
+    <row r="248" spans="1:26">
       <c r="K248" s="1"/>
-    </row>
-    <row r="249" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z248"/>
+    </row>
+    <row r="249" spans="1:26">
       <c r="K249" s="1"/>
-    </row>
-    <row r="250" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z249"/>
+    </row>
+    <row r="250" spans="1:26">
       <c r="K250" s="1"/>
-    </row>
-    <row r="251" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z250"/>
+    </row>
+    <row r="251" spans="1:26">
       <c r="K251" s="1"/>
-    </row>
-    <row r="252" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z251"/>
+    </row>
+    <row r="252" spans="1:26">
       <c r="K252" s="1"/>
-    </row>
-    <row r="253" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z252"/>
+    </row>
+    <row r="253" spans="1:26">
       <c r="K253" s="1"/>
-    </row>
-    <row r="254" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z253"/>
+    </row>
+    <row r="254" spans="1:26">
       <c r="K254" s="1"/>
-    </row>
-    <row r="255" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z254"/>
+    </row>
+    <row r="255" spans="1:26">
       <c r="K255" s="1"/>
-    </row>
-    <row r="256" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z255"/>
+    </row>
+    <row r="256" spans="1:26">
       <c r="K256" s="1"/>
-    </row>
-    <row r="257" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z256"/>
+    </row>
+    <row r="257" spans="1:26">
       <c r="K257" s="1"/>
-    </row>
-    <row r="258" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z257"/>
+    </row>
+    <row r="258" spans="1:26">
       <c r="K258" s="1"/>
-    </row>
-    <row r="259" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z258"/>
+    </row>
+    <row r="259" spans="1:26">
       <c r="K259" s="1"/>
-    </row>
-    <row r="260" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z259"/>
+    </row>
+    <row r="260" spans="1:26">
       <c r="K260" s="1"/>
-    </row>
-    <row r="261" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z260"/>
+    </row>
+    <row r="261" spans="1:26">
       <c r="K261" s="1"/>
-    </row>
-    <row r="262" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z261"/>
+    </row>
+    <row r="262" spans="1:26">
       <c r="K262" s="1"/>
-    </row>
-    <row r="263" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z262"/>
+    </row>
+    <row r="263" spans="1:26">
       <c r="K263" s="1"/>
-    </row>
-    <row r="264" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z263"/>
+    </row>
+    <row r="264" spans="1:26">
       <c r="K264" s="1"/>
-    </row>
-    <row r="265" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z264"/>
+    </row>
+    <row r="265" spans="1:26">
       <c r="K265" s="1"/>
-    </row>
-    <row r="266" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z265"/>
+    </row>
+    <row r="266" spans="1:26">
       <c r="K266" s="1"/>
-    </row>
-    <row r="267" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z266"/>
+    </row>
+    <row r="267" spans="1:26">
       <c r="K267" s="1"/>
-    </row>
-    <row r="268" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z267"/>
+    </row>
+    <row r="268" spans="1:26">
       <c r="K268" s="1"/>
-    </row>
-    <row r="269" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z268"/>
+    </row>
+    <row r="269" spans="1:26">
       <c r="K269" s="1"/>
-    </row>
-    <row r="270" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z269"/>
+    </row>
+    <row r="270" spans="1:26">
       <c r="K270" s="1"/>
-    </row>
-    <row r="271" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z270"/>
+    </row>
+    <row r="271" spans="1:26">
       <c r="K271" s="1"/>
-    </row>
-    <row r="272" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z271"/>
+    </row>
+    <row r="272" spans="1:26">
       <c r="K272" s="1"/>
-    </row>
-    <row r="273" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z272"/>
+    </row>
+    <row r="273" spans="1:26">
       <c r="K273" s="1"/>
-    </row>
-    <row r="274" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z273"/>
+    </row>
+    <row r="274" spans="1:26">
       <c r="K274" s="1"/>
-    </row>
-    <row r="275" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z274"/>
+    </row>
+    <row r="275" spans="1:26">
       <c r="K275" s="1"/>
-    </row>
-    <row r="276" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z275"/>
+    </row>
+    <row r="276" spans="1:26">
       <c r="K276" s="1"/>
-    </row>
-    <row r="277" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z276"/>
+    </row>
+    <row r="277" spans="1:26">
       <c r="K277" s="1"/>
-    </row>
-    <row r="278" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z277"/>
+    </row>
+    <row r="278" spans="1:26">
       <c r="K278" s="1"/>
-    </row>
-    <row r="279" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z278"/>
+    </row>
+    <row r="279" spans="1:26">
       <c r="K279" s="1"/>
-    </row>
-    <row r="280" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z279"/>
+    </row>
+    <row r="280" spans="1:26">
       <c r="K280" s="1"/>
-    </row>
-    <row r="281" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z280"/>
+    </row>
+    <row r="281" spans="1:26">
       <c r="K281" s="1"/>
-    </row>
-    <row r="282" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z281"/>
+    </row>
+    <row r="282" spans="1:26">
       <c r="K282" s="1"/>
-    </row>
-    <row r="283" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z282"/>
+    </row>
+    <row r="283" spans="1:26">
       <c r="K283" s="1"/>
-    </row>
-    <row r="284" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z283"/>
+    </row>
+    <row r="284" spans="1:26">
       <c r="K284" s="1"/>
-    </row>
-    <row r="285" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z284"/>
+    </row>
+    <row r="285" spans="1:26">
       <c r="K285" s="1"/>
-    </row>
-    <row r="286" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z285"/>
+    </row>
+    <row r="286" spans="1:26">
       <c r="K286" s="1"/>
-    </row>
-    <row r="287" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z286"/>
+    </row>
+    <row r="287" spans="1:26">
       <c r="K287" s="1"/>
-    </row>
-    <row r="288" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z287"/>
+    </row>
+    <row r="288" spans="1:26">
       <c r="K288" s="1"/>
-    </row>
-    <row r="289" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z288"/>
+    </row>
+    <row r="289" spans="1:26">
       <c r="K289" s="1"/>
-    </row>
-    <row r="290" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z289"/>
+    </row>
+    <row r="290" spans="1:26">
       <c r="K290" s="1"/>
-    </row>
-    <row r="291" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z290"/>
+    </row>
+    <row r="291" spans="1:26">
       <c r="K291" s="1"/>
-    </row>
-    <row r="292" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z291"/>
+    </row>
+    <row r="292" spans="1:26">
       <c r="K292" s="1"/>
-    </row>
-    <row r="293" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z292"/>
+    </row>
+    <row r="293" spans="1:26">
       <c r="K293" s="1"/>
-    </row>
-    <row r="294" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z293"/>
+    </row>
+    <row r="294" spans="1:26">
       <c r="K294" s="1"/>
-    </row>
-    <row r="295" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z294"/>
+    </row>
+    <row r="295" spans="1:26">
       <c r="K295" s="1"/>
-    </row>
-    <row r="296" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z295"/>
+    </row>
+    <row r="296" spans="1:26">
       <c r="K296" s="1"/>
-    </row>
-    <row r="297" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z296"/>
+    </row>
+    <row r="297" spans="1:26">
       <c r="K297" s="1"/>
-    </row>
-    <row r="298" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z297"/>
+    </row>
+    <row r="298" spans="1:26">
       <c r="K298" s="1"/>
-    </row>
-    <row r="299" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z298"/>
+    </row>
+    <row r="299" spans="1:26">
       <c r="K299" s="1"/>
-    </row>
-    <row r="300" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z299"/>
+    </row>
+    <row r="300" spans="1:26">
       <c r="K300" s="1"/>
-    </row>
-    <row r="301" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z300"/>
+    </row>
+    <row r="301" spans="1:26">
       <c r="K301" s="1"/>
-    </row>
-    <row r="302" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z301"/>
+    </row>
+    <row r="302" spans="1:26">
       <c r="K302" s="1"/>
-    </row>
-    <row r="303" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z302"/>
+    </row>
+    <row r="303" spans="1:26">
       <c r="K303" s="1"/>
-    </row>
-    <row r="304" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z303"/>
+    </row>
+    <row r="304" spans="1:26">
       <c r="K304" s="1"/>
-    </row>
-    <row r="305" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z304"/>
+    </row>
+    <row r="305" spans="1:26">
       <c r="K305" s="1"/>
-    </row>
-    <row r="306" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z305"/>
+    </row>
+    <row r="306" spans="1:26">
       <c r="K306" s="1"/>
-    </row>
-    <row r="307" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z306"/>
+    </row>
+    <row r="307" spans="1:26">
       <c r="K307" s="1"/>
-    </row>
-    <row r="308" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z307"/>
+    </row>
+    <row r="308" spans="1:26">
       <c r="K308" s="1"/>
-    </row>
-    <row r="309" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z308"/>
+    </row>
+    <row r="309" spans="1:26">
       <c r="K309" s="1"/>
-    </row>
-    <row r="310" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z309"/>
+    </row>
+    <row r="310" spans="1:26">
       <c r="K310" s="1"/>
-    </row>
-    <row r="311" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z310"/>
+    </row>
+    <row r="311" spans="1:26">
       <c r="K311" s="1"/>
-    </row>
-    <row r="312" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z311"/>
+    </row>
+    <row r="312" spans="1:26">
       <c r="K312" s="1"/>
-    </row>
-    <row r="313" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z312"/>
+    </row>
+    <row r="313" spans="1:26">
       <c r="K313" s="1"/>
-    </row>
-    <row r="314" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z313"/>
+    </row>
+    <row r="314" spans="1:26">
       <c r="K314" s="1"/>
-    </row>
-    <row r="315" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z314"/>
+    </row>
+    <row r="315" spans="1:26">
       <c r="K315" s="1"/>
-    </row>
-    <row r="316" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z315"/>
+    </row>
+    <row r="316" spans="1:26">
       <c r="K316" s="1"/>
-    </row>
-    <row r="317" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z316"/>
+    </row>
+    <row r="317" spans="1:26">
       <c r="K317" s="1"/>
-    </row>
-    <row r="318" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z317"/>
+    </row>
+    <row r="318" spans="1:26">
       <c r="K318" s="1"/>
-    </row>
-    <row r="319" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z318"/>
+    </row>
+    <row r="319" spans="1:26">
       <c r="K319" s="1"/>
-    </row>
-    <row r="320" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z319"/>
+    </row>
+    <row r="320" spans="1:26">
       <c r="K320" s="1"/>
-    </row>
-    <row r="321" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z320"/>
+    </row>
+    <row r="321" spans="1:26">
       <c r="K321" s="1"/>
-    </row>
-    <row r="322" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z321"/>
+    </row>
+    <row r="322" spans="1:26">
       <c r="K322" s="1"/>
-    </row>
-    <row r="323" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z322"/>
+    </row>
+    <row r="323" spans="1:26">
       <c r="K323" s="1"/>
-    </row>
-    <row r="324" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="Z323"/>
+    </row>
+    <row r="324" spans="1:26">
       <c r="K324" s="1"/>
+      <c r="Z324"/>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" r:id="rId1ps"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
   <ignoredErrors>
-    <ignoredError sqref="B2:B21" numberStoredAsText="1"/>
+    <ignoredError sqref="B2 B3 B4 B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21" numberStoredAsText="1"/>
   </ignoredErrors>
+  <tableParts count="0"/>
 </worksheet>
 </file>